--- a/data/stx_xlsx/BILL.ST.xlsx
+++ b/data/stx_xlsx/BILL.ST.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="471">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -907,6 +907,9 @@
   </si>
   <si>
     <t>Total current liabilities</t>
+  </si>
+  <si>
+    <t>Interest-bearing liabilities (Do not use)</t>
   </si>
   <si>
     <t>Provisions for pensions</t>
@@ -1554,7 +1557,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1638,6 +1641,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="7" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -15335,8 +15341,8 @@
       </c>
     </row>
     <row r="111" ht="15.0" customHeight="1">
-      <c r="A111" s="14" t="s">
-        <v>279</v>
+      <c r="A111" s="28" t="s">
+        <v>296</v>
       </c>
       <c r="B111" s="15"/>
       <c r="C111" s="15"/>
@@ -15433,8 +15439,8 @@
       <c r="W112" s="15"/>
     </row>
     <row r="113" ht="15.0" customHeight="1">
-      <c r="A113" s="14" t="s">
-        <v>279</v>
+      <c r="A113" s="28" t="s">
+        <v>296</v>
       </c>
       <c r="B113" s="16">
         <v>5080.25</v>
@@ -15475,7 +15481,7 @@
     </row>
     <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="14" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B114" s="16">
         <v>593.75</v>
@@ -15546,7 +15552,7 @@
     </row>
     <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="14" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B115" s="16">
         <v>4003.18</v>
@@ -15617,7 +15623,7 @@
     </row>
     <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B116" s="15"/>
       <c r="C116" s="16">
@@ -15686,7 +15692,7 @@
     </row>
     <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B117" s="15"/>
       <c r="C117" s="15"/>
@@ -15729,7 +15735,7 @@
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B118" s="15"/>
       <c r="C118" s="15"/>
@@ -15813,7 +15819,7 @@
     </row>
     <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B120" s="15"/>
       <c r="C120" s="15"/>
@@ -15871,7 +15877,7 @@
     </row>
     <row r="122" ht="15.0" customHeight="1">
       <c r="A122" s="14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B122" s="15"/>
       <c r="C122" s="15"/>
@@ -15904,7 +15910,7 @@
     </row>
     <row r="123" ht="15.0" customHeight="1">
       <c r="A123" s="14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B123" s="15"/>
       <c r="C123" s="15"/>
@@ -15945,7 +15951,7 @@
     </row>
     <row r="124" ht="15.0" customHeight="1">
       <c r="A124" s="14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B124" s="15"/>
       <c r="C124" s="15"/>
@@ -15978,7 +15984,7 @@
     </row>
     <row r="125" ht="15.0" customHeight="1">
       <c r="A125" s="14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B125" s="15"/>
       <c r="C125" s="15"/>
@@ -16019,7 +16025,7 @@
     </row>
     <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="17" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B126" s="18">
         <v>10315.76</v>
@@ -16090,7 +16096,7 @@
     </row>
     <row r="127" ht="15.0" customHeight="1">
       <c r="A127" s="14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B127" s="15"/>
       <c r="C127" s="15"/>
@@ -16131,7 +16137,7 @@
     </row>
     <row r="128" ht="15.0" customHeight="1">
       <c r="A128" s="17" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B128" s="18">
         <v>21482.25</v>
@@ -16202,7 +16208,7 @@
     </row>
     <row r="129" ht="15.0" customHeight="1">
       <c r="A129" s="14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B129" s="15"/>
       <c r="C129" s="16">
@@ -16271,7 +16277,7 @@
     </row>
     <row r="130" ht="15.0" customHeight="1">
       <c r="A130" s="14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B130" s="15"/>
       <c r="C130" s="16">
@@ -16340,7 +16346,7 @@
     </row>
     <row r="131" ht="15.0" customHeight="1">
       <c r="A131" s="14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B131" s="15"/>
       <c r="C131" s="16">
@@ -16379,7 +16385,7 @@
     </row>
     <row r="132" ht="15.0" customHeight="1">
       <c r="A132" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B132" s="15"/>
       <c r="C132" s="16">
@@ -16436,7 +16442,7 @@
     </row>
     <row r="133" ht="15.0" customHeight="1">
       <c r="A133" s="14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B133" s="15"/>
       <c r="C133" s="15"/>
@@ -16481,7 +16487,7 @@
     </row>
     <row r="134" ht="15.0" customHeight="1">
       <c r="A134" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B134" s="15"/>
       <c r="C134" s="16">
@@ -16520,7 +16526,7 @@
     </row>
     <row r="135" ht="15.0" customHeight="1">
       <c r="A135" s="14" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B135" s="15"/>
       <c r="C135" s="20">
@@ -16559,7 +16565,7 @@
     </row>
     <row r="136" ht="15.0" customHeight="1">
       <c r="A136" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B136" s="15"/>
       <c r="C136" s="15">
@@ -16628,7 +16634,7 @@
     </row>
     <row r="137" ht="15.0" customHeight="1">
       <c r="A137" s="17" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B137" s="18">
         <v>30336.05</v>
@@ -16756,7 +16762,7 @@
     </row>
     <row r="139" ht="15.0" customHeight="1">
       <c r="A139" s="17" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B139" s="18">
         <v>0.0</v>
@@ -16813,7 +16819,7 @@
     </row>
     <row r="140" ht="15.0" customHeight="1">
       <c r="A140" s="17" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B140" s="18">
         <v>30336.05</v>
@@ -16884,7 +16890,7 @@
     </row>
     <row r="141" ht="15.0" customHeight="1">
       <c r="A141" s="17" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B141" s="18">
         <v>51818.29</v>
@@ -16955,7 +16961,7 @@
     </row>
     <row r="142" ht="15.0" customHeight="1">
       <c r="A142" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B142" s="16">
         <v>248.7</v>
@@ -17026,7 +17032,7 @@
     </row>
     <row r="143" ht="15.0" customHeight="1">
       <c r="A143" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B143" s="22">
         <v>0.91</v>
@@ -17097,7 +17103,7 @@
     </row>
     <row r="144" ht="15.0" customHeight="1">
       <c r="A144" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B144" s="16">
         <v>249.61</v>
@@ -17168,7 +17174,7 @@
     </row>
     <row r="145" ht="15.0" customHeight="1">
       <c r="A145" s="14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B145" s="15"/>
       <c r="C145" s="15"/>
@@ -17201,7 +17207,7 @@
     </row>
     <row r="146" ht="15.0" customHeight="1">
       <c r="A146" s="14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B146" s="15"/>
       <c r="C146" s="15"/>
@@ -17252,7 +17258,7 @@
     </row>
     <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B147" s="15"/>
       <c r="C147" s="16">
@@ -17307,7 +17313,7 @@
     </row>
     <row r="148" ht="15.0" customHeight="1">
       <c r="A148" s="14" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B148" s="15"/>
       <c r="C148" s="16">
@@ -17354,7 +17360,7 @@
     </row>
     <row r="149" ht="15.0" customHeight="1">
       <c r="A149" s="14" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B149" s="15"/>
       <c r="C149" s="16">
@@ -17401,7 +17407,7 @@
     </row>
     <row r="150" ht="15.0" customHeight="1">
       <c r="A150" s="14" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B150" s="15"/>
       <c r="C150" s="15"/>
@@ -17436,7 +17442,7 @@
     </row>
     <row r="151" ht="15.0" customHeight="1">
       <c r="A151" s="14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B151" s="15"/>
       <c r="C151" s="16">
@@ -17475,7 +17481,7 @@
     </row>
     <row r="152" ht="15.0" customHeight="1">
       <c r="A152" s="14" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B152" s="15"/>
       <c r="C152" s="16">
@@ -17514,7 +17520,7 @@
     </row>
     <row r="153" ht="15.0" customHeight="1">
       <c r="A153" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B153" s="15"/>
       <c r="C153" s="16">
@@ -17553,7 +17559,7 @@
     </row>
     <row r="154" ht="15.0" customHeight="1">
       <c r="A154" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B154" s="16">
         <v>249.61</v>
@@ -17624,7 +17630,7 @@
     </row>
     <row r="155" ht="15.0" customHeight="1">
       <c r="A155" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B155" s="22">
         <v>0.91</v>
@@ -17695,7 +17701,7 @@
     </row>
     <row r="156" ht="15.0" customHeight="1">
       <c r="A156" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B156" s="16">
         <v>248.7</v>
@@ -17766,7 +17772,7 @@
     </row>
     <row r="157" ht="15.0" customHeight="1">
       <c r="A157" s="14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B157" s="22">
         <v>1.0</v>
@@ -18699,7 +18705,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -19085,70 +19091,70 @@
         <v>44</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -19224,7 +19230,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -19322,7 +19328,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B20" s="16">
         <v>942.65</v>
@@ -19393,7 +19399,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B21" s="22">
         <v>29.66</v>
@@ -19422,7 +19428,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B22" s="20">
         <v>-272.2</v>
@@ -19491,7 +19497,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B23" s="20">
         <v>-139.81</v>
@@ -19520,7 +19526,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B24" s="21">
         <v>-25.42</v>
@@ -19553,7 +19559,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -19584,7 +19590,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B26" s="15"/>
       <c r="C26" s="21">
@@ -19615,7 +19621,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B27" s="16">
         <v>2823.73</v>
@@ -19670,7 +19676,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -19727,7 +19733,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B29" s="16">
         <v>3037.68</v>
@@ -19766,7 +19772,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -19829,7 +19835,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B31" s="16">
         <v>310.33</v>
@@ -19898,7 +19904,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B32" s="20">
         <v>-187.47</v>
@@ -19951,7 +19957,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B33" s="20">
         <v>-328.34</v>
@@ -20047,7 +20053,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -20084,7 +20090,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B36" s="21">
         <v>-14.83</v>
@@ -20117,7 +20123,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B37" s="15"/>
       <c r="C37" s="15"/>
@@ -20152,7 +20158,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>
@@ -20212,7 +20218,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B40" s="15"/>
       <c r="C40" s="15"/>
@@ -20241,7 +20247,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B41" s="15"/>
       <c r="C41" s="15"/>
@@ -20270,7 +20276,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
@@ -20305,7 +20311,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B43" s="15"/>
       <c r="C43" s="15"/>
@@ -20334,7 +20340,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B44" s="15"/>
       <c r="C44" s="15"/>
@@ -20363,7 +20369,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B45" s="15"/>
       <c r="C45" s="15"/>
@@ -20402,7 +20408,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
@@ -20431,7 +20437,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B47" s="15"/>
       <c r="C47" s="15"/>
@@ -20460,7 +20466,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
@@ -20503,7 +20509,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B49" s="15"/>
       <c r="C49" s="15"/>
@@ -20534,7 +20540,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B50" s="15"/>
       <c r="C50" s="15"/>
@@ -20563,7 +20569,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B51" s="15"/>
       <c r="C51" s="15"/>
@@ -20592,7 +20598,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B52" s="15"/>
       <c r="C52" s="15"/>
@@ -20625,7 +20631,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B53" s="15"/>
       <c r="C53" s="16">
@@ -20662,7 +20668,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B54" s="15"/>
       <c r="C54" s="20">
@@ -20729,7 +20735,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B55" s="15"/>
       <c r="C55" s="20">
@@ -20796,7 +20802,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B56" s="15"/>
       <c r="C56" s="16">
@@ -20863,7 +20869,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B57" s="15"/>
       <c r="C57" s="15"/>
@@ -20892,7 +20898,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B58" s="15"/>
       <c r="C58" s="15"/>
@@ -20921,7 +20927,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="17" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B59" s="19">
         <v>3354.37</v>
@@ -20992,7 +20998,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B60" s="20">
         <v>-2813.14</v>
@@ -21035,7 +21041,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B61" s="15"/>
       <c r="C61" s="15"/>
@@ -21096,7 +21102,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B62" s="22">
         <v>23.3</v>
@@ -21167,7 +21173,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B63" s="15"/>
       <c r="C63" s="15"/>
@@ -21210,7 +21216,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B64" s="15"/>
       <c r="C64" s="15">
@@ -21267,7 +21273,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B65" s="21">
         <v>-4.24</v>
@@ -21332,7 +21338,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B66" s="22">
         <v>24.36</v>
@@ -21371,7 +21377,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B67" s="15"/>
       <c r="C67" s="15">
@@ -21412,7 +21418,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B68" s="15"/>
       <c r="C68" s="15"/>
@@ -21447,7 +21453,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B69" s="15"/>
       <c r="C69" s="15">
@@ -21478,7 +21484,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B70" s="15"/>
       <c r="C70" s="15"/>
@@ -21519,7 +21525,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B71" s="15"/>
       <c r="C71" s="15"/>
@@ -21552,7 +21558,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="17" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B72" s="23">
         <v>-2769.71</v>
@@ -21623,7 +21629,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B73" s="15"/>
       <c r="C73" s="15"/>
@@ -21672,7 +21678,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B74" s="15"/>
       <c r="C74" s="16">
@@ -21711,7 +21717,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B75" s="20">
         <v>-239.37</v>
@@ -21752,7 +21758,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B76" s="15">
         <v>0.0</v>
@@ -21821,7 +21827,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B77" s="15"/>
       <c r="C77" s="15"/>
@@ -21856,7 +21862,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="14" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B78" s="15"/>
       <c r="C78" s="15"/>
@@ -21895,7 +21901,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B79" s="15"/>
       <c r="C79" s="15"/>
@@ -21950,7 +21956,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="14" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B80" s="15"/>
       <c r="C80" s="15"/>
@@ -21985,7 +21991,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B81" s="15"/>
       <c r="C81" s="15"/>
@@ -22016,7 +22022,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="14" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B82" s="15"/>
       <c r="C82" s="15"/>
@@ -22059,7 +22065,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B83" s="15"/>
       <c r="C83" s="15"/>
@@ -22102,7 +22108,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="14" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B84" s="15"/>
       <c r="C84" s="15"/>
@@ -22137,7 +22143,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B85" s="15"/>
       <c r="C85" s="15"/>
@@ -22166,7 +22172,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="17" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B86" s="23">
         <v>-239.37</v>
@@ -22237,7 +22243,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="14" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B87" s="16">
         <v>1272.8</v>
@@ -22308,7 +22314,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="14" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B88" s="20">
         <v>-221.37</v>
@@ -22379,7 +22385,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="14" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B89" s="16">
         <v>1400.73</v>
@@ -22450,7 +22456,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="14" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B90" s="20">
         <v>-1134.36</v>
@@ -22495,7 +22501,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="17" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B91" s="19">
         <v>123.92</v>
@@ -22566,7 +22572,7 @@
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B92" s="15"/>
       <c r="C92" s="15"/>
@@ -22609,7 +22615,7 @@
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="14" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B93" s="15"/>
       <c r="C93" s="15"/>
@@ -22642,7 +22648,7 @@
     </row>
     <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="14" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B94" s="15"/>
       <c r="C94" s="16">
@@ -22681,7 +22687,7 @@
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="14" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B95" s="15"/>
       <c r="C95" s="20">
@@ -23644,7 +23650,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -23812,16 +23818,16 @@
         <v>39</v>
       </c>
       <c r="W11" s="7" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
@@ -24226,7 +24232,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -24322,3015 +24328,3015 @@
         <v>70</v>
       </c>
       <c r="W19" s="13" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="X19" s="13" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Y19" s="13" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Z19" s="13" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="28" t="s">
-        <v>419</v>
-      </c>
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29"/>
-      <c r="K20" s="29"/>
-      <c r="L20" s="29"/>
-      <c r="M20" s="29"/>
-      <c r="N20" s="29"/>
-      <c r="O20" s="29"/>
-      <c r="P20" s="29"/>
-      <c r="Q20" s="29"/>
-      <c r="R20" s="29"/>
-      <c r="S20" s="29"/>
-      <c r="T20" s="29"/>
-      <c r="U20" s="29"/>
-      <c r="V20" s="29"/>
-      <c r="W20" s="29"/>
-      <c r="X20" s="29"/>
-      <c r="Y20" s="29"/>
-      <c r="Z20" s="29"/>
+      <c r="A20" s="29" t="s">
+        <v>420</v>
+      </c>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="30"/>
+      <c r="Q20" s="30"/>
+      <c r="R20" s="30"/>
+      <c r="S20" s="30"/>
+      <c r="T20" s="30"/>
+      <c r="U20" s="30"/>
+      <c r="V20" s="30"/>
+      <c r="W20" s="30"/>
+      <c r="X20" s="30"/>
+      <c r="Y20" s="30"/>
+      <c r="Z20" s="30"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="30" t="s">
-        <v>419</v>
-      </c>
-      <c r="B21" s="31">
+      <c r="A21" s="31" t="s">
+        <v>420</v>
+      </c>
+      <c r="B21" s="32">
         <v>31578.57</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="32">
         <v>31042.79</v>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="32">
         <v>33051.22</v>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="32">
         <v>37715.44</v>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="32">
         <v>36400.22</v>
       </c>
-      <c r="G21" s="31">
+      <c r="G21" s="32">
         <v>25940.0</v>
       </c>
-      <c r="H21" s="31">
+      <c r="H21" s="32">
         <v>29798.07</v>
       </c>
-      <c r="I21" s="31">
+      <c r="I21" s="32">
         <v>34246.01</v>
       </c>
-      <c r="J21" s="31">
+      <c r="J21" s="32">
         <v>33171.84</v>
       </c>
-      <c r="K21" s="31">
+      <c r="K21" s="32">
         <v>38831.87</v>
       </c>
-      <c r="L21" s="31">
+      <c r="L21" s="32">
         <v>28626.36</v>
       </c>
-      <c r="M21" s="31">
+      <c r="M21" s="32">
         <v>23219.14</v>
       </c>
-      <c r="N21" s="31">
+      <c r="N21" s="32">
         <v>17255.41</v>
       </c>
-      <c r="O21" s="32">
+      <c r="O21" s="33">
         <v>5226.92</v>
       </c>
-      <c r="P21" s="32">
+      <c r="P21" s="33">
         <v>5478.92</v>
       </c>
-      <c r="Q21" s="32">
+      <c r="Q21" s="33">
         <v>5372.53</v>
       </c>
-      <c r="R21" s="32">
+      <c r="R21" s="33">
         <v>3169.98</v>
       </c>
-      <c r="S21" s="32">
+      <c r="S21" s="33">
         <v>5030.28</v>
       </c>
-      <c r="T21" s="32">
+      <c r="T21" s="33">
         <v>8030.73</v>
       </c>
-      <c r="U21" s="32">
+      <c r="U21" s="33">
         <v>6698.42</v>
       </c>
-      <c r="V21" s="32">
+      <c r="V21" s="33">
         <v>6989.64</v>
       </c>
-      <c r="W21" s="32">
+      <c r="W21" s="33">
         <v>6860.59</v>
       </c>
-      <c r="X21" s="32">
+      <c r="X21" s="33">
         <v>5819.89</v>
       </c>
-      <c r="Y21" s="32">
+      <c r="Y21" s="33">
         <v>5230.18</v>
       </c>
-      <c r="Z21" s="31"/>
+      <c r="Z21" s="32"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="30" t="s">
-        <v>420</v>
-      </c>
-      <c r="B22" s="31">
+      <c r="A22" s="31" t="s">
+        <v>421</v>
+      </c>
+      <c r="B22" s="32">
         <v>35003.36</v>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="32">
         <v>33662.77</v>
       </c>
-      <c r="D22" s="31">
+      <c r="D22" s="32">
         <v>31416.4</v>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="32">
         <v>32344.92</v>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="32">
         <v>33886.96</v>
       </c>
-      <c r="G22" s="31">
+      <c r="G22" s="32">
         <v>30850.5</v>
       </c>
-      <c r="H22" s="31">
+      <c r="H22" s="32">
         <v>32536.85</v>
       </c>
-      <c r="I22" s="31">
+      <c r="I22" s="32">
         <v>32182.85</v>
       </c>
-      <c r="J22" s="31">
+      <c r="J22" s="32">
         <v>27831.99</v>
       </c>
-      <c r="K22" s="31">
+      <c r="K22" s="32">
         <v>24654.54</v>
       </c>
-      <c r="L22" s="31">
+      <c r="L22" s="32">
         <v>16677.65</v>
       </c>
-      <c r="M22" s="31">
+      <c r="M22" s="32">
         <v>12020.6</v>
       </c>
-      <c r="N22" s="32">
+      <c r="N22" s="33">
         <v>7310.64</v>
       </c>
-      <c r="O22" s="32">
+      <c r="O22" s="33">
         <v>4950.22</v>
       </c>
-      <c r="P22" s="32">
+      <c r="P22" s="33">
         <v>5435.13</v>
       </c>
-      <c r="Q22" s="32">
+      <c r="Q22" s="33">
         <v>5323.05</v>
       </c>
-      <c r="R22" s="32">
+      <c r="R22" s="33">
         <v>6030.18</v>
       </c>
-      <c r="S22" s="32">
+      <c r="S22" s="33">
         <v>6348.24</v>
       </c>
-      <c r="T22" s="32">
+      <c r="T22" s="33">
         <v>7111.79</v>
       </c>
-      <c r="U22" s="32">
+      <c r="U22" s="33">
         <v>6172.02</v>
       </c>
-      <c r="V22" s="31"/>
-      <c r="W22" s="31"/>
-      <c r="X22" s="31"/>
-      <c r="Y22" s="31"/>
-      <c r="Z22" s="31"/>
+      <c r="V22" s="32"/>
+      <c r="W22" s="32"/>
+      <c r="X22" s="32"/>
+      <c r="Y22" s="32"/>
+      <c r="Z22" s="32"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="28" t="s">
-        <v>421</v>
-      </c>
-      <c r="B23" s="29"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="29"/>
-      <c r="K23" s="29"/>
-      <c r="L23" s="29"/>
-      <c r="M23" s="29"/>
-      <c r="N23" s="29"/>
-      <c r="O23" s="29"/>
-      <c r="P23" s="29"/>
-      <c r="Q23" s="29"/>
-      <c r="R23" s="29"/>
-      <c r="S23" s="29"/>
-      <c r="T23" s="29"/>
-      <c r="U23" s="29"/>
-      <c r="V23" s="29"/>
-      <c r="W23" s="29"/>
-      <c r="X23" s="29"/>
-      <c r="Y23" s="29"/>
-      <c r="Z23" s="29"/>
+      <c r="A23" s="29" t="s">
+        <v>422</v>
+      </c>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="30"/>
+      <c r="P23" s="30"/>
+      <c r="Q23" s="30"/>
+      <c r="R23" s="30"/>
+      <c r="S23" s="30"/>
+      <c r="T23" s="30"/>
+      <c r="U23" s="30"/>
+      <c r="V23" s="30"/>
+      <c r="W23" s="30"/>
+      <c r="X23" s="30"/>
+      <c r="Y23" s="30"/>
+      <c r="Z23" s="30"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="30" t="s">
-        <v>421</v>
-      </c>
-      <c r="B24" s="31">
+      <c r="A24" s="31" t="s">
+        <v>422</v>
+      </c>
+      <c r="B24" s="32">
         <v>26021.72</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="32">
         <v>25733.12</v>
       </c>
-      <c r="D24" s="31">
+      <c r="D24" s="32">
         <v>29862.21</v>
       </c>
-      <c r="E24" s="31">
+      <c r="E24" s="32">
         <v>34628.92</v>
       </c>
-      <c r="F24" s="31">
+      <c r="F24" s="32">
         <v>31645.97</v>
       </c>
-      <c r="G24" s="31">
+      <c r="G24" s="32">
         <v>21603.31</v>
       </c>
-      <c r="H24" s="31">
+      <c r="H24" s="32">
         <v>21436.9</v>
       </c>
-      <c r="I24" s="31">
+      <c r="I24" s="32">
         <v>29273.8</v>
       </c>
-      <c r="J24" s="31">
+      <c r="J24" s="32">
         <v>30211.19</v>
       </c>
-      <c r="K24" s="31">
+      <c r="K24" s="32">
         <v>34256.3</v>
       </c>
-      <c r="L24" s="31">
+      <c r="L24" s="32">
         <v>22452.65</v>
       </c>
-      <c r="M24" s="31">
+      <c r="M24" s="32">
         <v>15944.33</v>
       </c>
-      <c r="N24" s="31">
+      <c r="N24" s="32">
         <v>10917.36</v>
       </c>
-      <c r="O24" s="32">
+      <c r="O24" s="33">
         <v>5321.5</v>
       </c>
-      <c r="P24" s="32">
+      <c r="P24" s="33">
         <v>5298.45</v>
       </c>
-      <c r="Q24" s="32">
+      <c r="Q24" s="33">
         <v>4596.59</v>
       </c>
-      <c r="R24" s="32">
+      <c r="R24" s="33">
         <v>1005.6</v>
       </c>
-      <c r="S24" s="32">
+      <c r="S24" s="33">
         <v>2983.28</v>
       </c>
-      <c r="T24" s="32">
+      <c r="T24" s="33">
         <v>5892.82</v>
       </c>
-      <c r="U24" s="32">
+      <c r="U24" s="33">
         <v>4702.9</v>
       </c>
-      <c r="V24" s="32">
+      <c r="V24" s="33">
         <v>5763.88</v>
       </c>
-      <c r="W24" s="32">
+      <c r="W24" s="33">
         <v>5825.04</v>
       </c>
-      <c r="X24" s="32">
+      <c r="X24" s="33">
         <v>4756.85</v>
       </c>
-      <c r="Y24" s="32">
+      <c r="Y24" s="33">
         <v>3814.03</v>
       </c>
-      <c r="Z24" s="31"/>
+      <c r="Z24" s="32"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="30" t="s">
-        <v>422</v>
-      </c>
-      <c r="B25" s="31">
+      <c r="A25" s="31" t="s">
+        <v>423</v>
+      </c>
+      <c r="B25" s="32">
         <v>30523.33</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="32">
         <v>29432.74</v>
       </c>
-      <c r="D25" s="31">
+      <c r="D25" s="32">
         <v>26841.47</v>
       </c>
-      <c r="E25" s="31">
+      <c r="E25" s="32">
         <v>27301.47</v>
       </c>
-      <c r="F25" s="31">
+      <c r="F25" s="32">
         <v>28491.16</v>
       </c>
-      <c r="G25" s="31">
+      <c r="G25" s="32">
         <v>26039.17</v>
       </c>
-      <c r="H25" s="31">
+      <c r="H25" s="32">
         <v>27175.08</v>
       </c>
-      <c r="I25" s="31">
+      <c r="I25" s="32">
         <v>26854.81</v>
       </c>
-      <c r="J25" s="31">
+      <c r="J25" s="32">
         <v>22320.74</v>
       </c>
-      <c r="K25" s="31">
+      <c r="K25" s="32">
         <v>19248.62</v>
       </c>
-      <c r="L25" s="31">
+      <c r="L25" s="32">
         <v>12524.84</v>
       </c>
-      <c r="M25" s="32">
+      <c r="M25" s="33">
         <v>8970.63</v>
       </c>
-      <c r="N25" s="32">
+      <c r="N25" s="33">
         <v>5445.18</v>
       </c>
-      <c r="O25" s="32">
+      <c r="O25" s="33">
         <v>3921.81</v>
       </c>
-      <c r="P25" s="32">
+      <c r="P25" s="33">
         <v>3980.42</v>
       </c>
-      <c r="Q25" s="32">
+      <c r="Q25" s="33">
         <v>3619.88</v>
       </c>
-      <c r="R25" s="32">
+      <c r="R25" s="33">
         <v>4090.24</v>
       </c>
-      <c r="S25" s="32">
+      <c r="S25" s="33">
         <v>4735.03</v>
       </c>
-      <c r="T25" s="32">
+      <c r="T25" s="33">
         <v>5565.9</v>
       </c>
-      <c r="U25" s="32">
+      <c r="U25" s="33">
         <v>4848.19</v>
       </c>
-      <c r="V25" s="31"/>
-      <c r="W25" s="31"/>
-      <c r="X25" s="31"/>
-      <c r="Y25" s="31"/>
-      <c r="Z25" s="31"/>
+      <c r="V25" s="32"/>
+      <c r="W25" s="32"/>
+      <c r="X25" s="32"/>
+      <c r="Y25" s="32"/>
+      <c r="Z25" s="32"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="28" t="s">
-        <v>423</v>
-      </c>
-      <c r="B26" s="29"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="29"/>
-      <c r="L26" s="29"/>
-      <c r="M26" s="29"/>
-      <c r="N26" s="29"/>
-      <c r="O26" s="29"/>
-      <c r="P26" s="29"/>
-      <c r="Q26" s="29"/>
-      <c r="R26" s="29"/>
-      <c r="S26" s="29"/>
-      <c r="T26" s="29"/>
-      <c r="U26" s="29"/>
-      <c r="V26" s="29"/>
-      <c r="W26" s="29"/>
-      <c r="X26" s="29"/>
-      <c r="Y26" s="29"/>
-      <c r="Z26" s="29"/>
+      <c r="A26" s="29" t="s">
+        <v>424</v>
+      </c>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+      <c r="M26" s="30"/>
+      <c r="N26" s="30"/>
+      <c r="O26" s="30"/>
+      <c r="P26" s="30"/>
+      <c r="Q26" s="30"/>
+      <c r="R26" s="30"/>
+      <c r="S26" s="30"/>
+      <c r="T26" s="30"/>
+      <c r="U26" s="30"/>
+      <c r="V26" s="30"/>
+      <c r="W26" s="30"/>
+      <c r="X26" s="30"/>
+      <c r="Y26" s="30"/>
+      <c r="Z26" s="30"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="30" t="s">
-        <v>424</v>
-      </c>
-      <c r="B27" s="32">
+      <c r="A27" s="31" t="s">
+        <v>425</v>
+      </c>
+      <c r="B27" s="33">
         <v>104.25</v>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="33">
         <v>103.09</v>
       </c>
-      <c r="D27" s="32">
+      <c r="D27" s="33">
         <v>119.63</v>
       </c>
-      <c r="E27" s="32">
+      <c r="E27" s="33">
         <v>154.93</v>
       </c>
-      <c r="F27" s="32">
+      <c r="F27" s="33">
         <v>141.58</v>
       </c>
-      <c r="G27" s="33">
+      <c r="G27" s="34">
         <v>96.65</v>
       </c>
-      <c r="H27" s="33">
+      <c r="H27" s="34">
         <v>95.91</v>
       </c>
-      <c r="I27" s="32">
+      <c r="I27" s="33">
         <v>130.97</v>
       </c>
-      <c r="J27" s="32">
+      <c r="J27" s="33">
         <v>135.17</v>
       </c>
-      <c r="K27" s="32">
+      <c r="K27" s="33">
         <v>153.26</v>
       </c>
-      <c r="L27" s="32">
+      <c r="L27" s="33">
         <v>100.45</v>
       </c>
-      <c r="M27" s="33">
+      <c r="M27" s="34">
         <v>71.34</v>
       </c>
-      <c r="N27" s="33">
+      <c r="N27" s="34">
         <v>48.84</v>
       </c>
-      <c r="O27" s="33">
+      <c r="O27" s="34">
         <v>38.06</v>
       </c>
-      <c r="P27" s="33">
+      <c r="P27" s="34">
         <v>37.89</v>
       </c>
-      <c r="Q27" s="33">
+      <c r="Q27" s="34">
         <v>32.3</v>
       </c>
-      <c r="R27" s="33">
+      <c r="R27" s="34">
         <v>10.0</v>
       </c>
-      <c r="S27" s="33">
+      <c r="S27" s="34">
         <v>29.66</v>
       </c>
-      <c r="T27" s="33">
+      <c r="T27" s="34">
         <v>58.67</v>
       </c>
-      <c r="U27" s="33">
+      <c r="U27" s="34">
         <v>46.84</v>
       </c>
-      <c r="V27" s="33">
+      <c r="V27" s="34">
         <v>57.4</v>
       </c>
-      <c r="W27" s="31"/>
-      <c r="X27" s="31"/>
-      <c r="Y27" s="31"/>
-      <c r="Z27" s="31"/>
+      <c r="W27" s="32"/>
+      <c r="X27" s="32"/>
+      <c r="Y27" s="32"/>
+      <c r="Z27" s="32"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="30" t="s">
-        <v>425</v>
-      </c>
-      <c r="B28" s="32">
+      <c r="A28" s="31" t="s">
+        <v>426</v>
+      </c>
+      <c r="B28" s="33">
         <v>128.62</v>
       </c>
-      <c r="C28" s="32">
+      <c r="C28" s="33">
         <v>126.29</v>
       </c>
-      <c r="D28" s="32">
+      <c r="D28" s="33">
         <v>117.3</v>
       </c>
-      <c r="E28" s="32">
+      <c r="E28" s="33">
         <v>122.15</v>
       </c>
-      <c r="F28" s="32">
+      <c r="F28" s="33">
         <v>127.47</v>
       </c>
-      <c r="G28" s="32">
+      <c r="G28" s="33">
         <v>116.5</v>
       </c>
-      <c r="H28" s="32">
+      <c r="H28" s="33">
         <v>121.58</v>
       </c>
-      <c r="I28" s="32">
+      <c r="I28" s="33">
         <v>120.15</v>
       </c>
-      <c r="J28" s="33">
+      <c r="J28" s="34">
         <v>99.86</v>
       </c>
-      <c r="K28" s="33">
+      <c r="K28" s="34">
         <v>89.56</v>
       </c>
-      <c r="L28" s="33">
+      <c r="L28" s="34">
         <v>62.32</v>
       </c>
-      <c r="M28" s="33">
+      <c r="M28" s="34">
         <v>49.05</v>
       </c>
-      <c r="N28" s="33">
+      <c r="N28" s="34">
         <v>33.51</v>
       </c>
-      <c r="O28" s="33">
+      <c r="O28" s="34">
         <v>30.19</v>
       </c>
-      <c r="P28" s="33">
+      <c r="P28" s="34">
         <v>33.76</v>
       </c>
-      <c r="Q28" s="33">
+      <c r="Q28" s="34">
         <v>33.34</v>
       </c>
-      <c r="R28" s="33">
+      <c r="R28" s="34">
         <v>40.72</v>
       </c>
-      <c r="S28" s="31"/>
-      <c r="T28" s="31"/>
-      <c r="U28" s="31"/>
-      <c r="V28" s="31"/>
-      <c r="W28" s="31"/>
-      <c r="X28" s="31"/>
-      <c r="Y28" s="31"/>
-      <c r="Z28" s="31"/>
+      <c r="S28" s="32"/>
+      <c r="T28" s="32"/>
+      <c r="U28" s="32"/>
+      <c r="V28" s="32"/>
+      <c r="W28" s="32"/>
+      <c r="X28" s="32"/>
+      <c r="Y28" s="32"/>
+      <c r="Z28" s="32"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="28" t="s">
-        <v>426</v>
-      </c>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="29"/>
-      <c r="J29" s="29"/>
-      <c r="K29" s="29"/>
-      <c r="L29" s="29"/>
-      <c r="M29" s="29"/>
-      <c r="N29" s="29"/>
-      <c r="O29" s="29"/>
-      <c r="P29" s="29"/>
-      <c r="Q29" s="29"/>
-      <c r="R29" s="29"/>
-      <c r="S29" s="29"/>
-      <c r="T29" s="29"/>
-      <c r="U29" s="29"/>
-      <c r="V29" s="29"/>
-      <c r="W29" s="29"/>
-      <c r="X29" s="29"/>
-      <c r="Y29" s="29"/>
-      <c r="Z29" s="29"/>
+      <c r="A29" s="29" t="s">
+        <v>427</v>
+      </c>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="30"/>
+      <c r="P29" s="30"/>
+      <c r="Q29" s="30"/>
+      <c r="R29" s="30"/>
+      <c r="S29" s="30"/>
+      <c r="T29" s="30"/>
+      <c r="U29" s="30"/>
+      <c r="V29" s="30"/>
+      <c r="W29" s="30"/>
+      <c r="X29" s="30"/>
+      <c r="Y29" s="30"/>
+      <c r="Z29" s="30"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="30" t="s">
-        <v>427</v>
-      </c>
-      <c r="B30" s="34">
+      <c r="A30" s="31" t="s">
+        <v>428</v>
+      </c>
+      <c r="B30" s="35">
         <v>2.35</v>
       </c>
-      <c r="C30" s="34">
+      <c r="C30" s="35">
         <v>0.44</v>
       </c>
-      <c r="D30" s="34">
+      <c r="D30" s="35">
         <v>12.05</v>
       </c>
-      <c r="E30" s="34">
+      <c r="E30" s="35">
         <v>6.7</v>
       </c>
-      <c r="F30" s="34">
+      <c r="F30" s="35">
         <v>3.59</v>
       </c>
-      <c r="G30" s="35">
+      <c r="G30" s="36">
         <v>-2.4</v>
       </c>
-      <c r="H30" s="35">
+      <c r="H30" s="36">
         <v>-11.97</v>
       </c>
-      <c r="I30" s="35">
+      <c r="I30" s="36">
         <v>-3.02</v>
       </c>
-      <c r="J30" s="34">
+      <c r="J30" s="35">
         <v>6.74</v>
       </c>
-      <c r="K30" s="34">
+      <c r="K30" s="35">
         <v>6.11</v>
       </c>
-      <c r="L30" s="34">
+      <c r="L30" s="35">
         <v>7.43</v>
       </c>
-      <c r="M30" s="34">
+      <c r="M30" s="35">
         <v>2.65</v>
       </c>
-      <c r="N30" s="34">
+      <c r="N30" s="35">
         <v>0.58</v>
       </c>
-      <c r="O30" s="34">
+      <c r="O30" s="35">
         <v>13.32</v>
       </c>
-      <c r="P30" s="34">
+      <c r="P30" s="35">
         <v>17.61</v>
       </c>
-      <c r="Q30" s="34">
+      <c r="Q30" s="35">
         <v>13.49</v>
       </c>
-      <c r="R30" s="34">
+      <c r="R30" s="35">
         <v>16.86</v>
       </c>
-      <c r="S30" s="34">
+      <c r="S30" s="35">
         <v>2.25</v>
       </c>
-      <c r="T30" s="34">
+      <c r="T30" s="35">
         <v>2.41</v>
       </c>
-      <c r="U30" s="35">
+      <c r="U30" s="36">
         <v>-12.4</v>
       </c>
-      <c r="V30" s="34">
+      <c r="V30" s="35">
         <v>10.22</v>
       </c>
-      <c r="W30" s="34"/>
-      <c r="X30" s="34"/>
-      <c r="Y30" s="34"/>
-      <c r="Z30" s="34"/>
+      <c r="W30" s="35"/>
+      <c r="X30" s="35"/>
+      <c r="Y30" s="35"/>
+      <c r="Z30" s="35"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="30" t="s">
-        <v>428</v>
-      </c>
-      <c r="B31" s="34">
+      <c r="A31" s="31" t="s">
+        <v>429</v>
+      </c>
+      <c r="B31" s="35">
         <v>5.38</v>
       </c>
-      <c r="C31" s="34">
+      <c r="C31" s="35">
         <v>4.6</v>
       </c>
-      <c r="D31" s="34">
+      <c r="D31" s="35">
         <v>2.67</v>
       </c>
-      <c r="E31" s="35">
+      <c r="E31" s="36">
         <v>-0.42</v>
       </c>
-      <c r="F31" s="35">
+      <c r="F31" s="36">
         <v>-0.61</v>
       </c>
-      <c r="G31" s="34">
+      <c r="G31" s="35">
         <v>0.06</v>
       </c>
-      <c r="H31" s="34">
+      <c r="H31" s="35">
         <v>1.7</v>
       </c>
-      <c r="I31" s="34">
+      <c r="I31" s="35">
         <v>4.06</v>
       </c>
-      <c r="J31" s="34">
+      <c r="J31" s="35">
         <v>5.45</v>
       </c>
-      <c r="K31" s="34">
+      <c r="K31" s="35">
         <v>5.82</v>
       </c>
-      <c r="L31" s="34">
+      <c r="L31" s="35">
         <v>7.28</v>
       </c>
-      <c r="M31" s="34">
+      <c r="M31" s="35">
         <v>8.17</v>
       </c>
-      <c r="N31" s="34">
+      <c r="N31" s="35">
         <v>10.8</v>
       </c>
-      <c r="O31" s="34">
+      <c r="O31" s="35">
         <v>12.42</v>
       </c>
-      <c r="P31" s="34">
+      <c r="P31" s="35">
         <v>8.9</v>
       </c>
-      <c r="Q31" s="34">
+      <c r="Q31" s="35">
         <v>1.35</v>
       </c>
-      <c r="R31" s="34">
+      <c r="R31" s="35">
         <v>1.67</v>
       </c>
-      <c r="S31" s="34"/>
-      <c r="T31" s="34"/>
-      <c r="U31" s="34"/>
-      <c r="V31" s="34"/>
-      <c r="W31" s="34"/>
-      <c r="X31" s="34"/>
-      <c r="Y31" s="34"/>
-      <c r="Z31" s="34"/>
+      <c r="S31" s="35"/>
+      <c r="T31" s="35"/>
+      <c r="U31" s="35"/>
+      <c r="V31" s="35"/>
+      <c r="W31" s="35"/>
+      <c r="X31" s="35"/>
+      <c r="Y31" s="35"/>
+      <c r="Z31" s="35"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="28" t="s">
-        <v>429</v>
-      </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="29"/>
-      <c r="L32" s="29"/>
-      <c r="M32" s="29"/>
-      <c r="N32" s="29"/>
-      <c r="O32" s="29"/>
-      <c r="P32" s="29"/>
-      <c r="Q32" s="29"/>
-      <c r="R32" s="29"/>
-      <c r="S32" s="29"/>
-      <c r="T32" s="29"/>
-      <c r="U32" s="29"/>
-      <c r="V32" s="29"/>
-      <c r="W32" s="29"/>
-      <c r="X32" s="29"/>
-      <c r="Y32" s="29"/>
-      <c r="Z32" s="29"/>
+      <c r="A32" s="29" t="s">
+        <v>430</v>
+      </c>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="30"/>
+      <c r="P32" s="30"/>
+      <c r="Q32" s="30"/>
+      <c r="R32" s="30"/>
+      <c r="S32" s="30"/>
+      <c r="T32" s="30"/>
+      <c r="U32" s="30"/>
+      <c r="V32" s="30"/>
+      <c r="W32" s="30"/>
+      <c r="X32" s="30"/>
+      <c r="Y32" s="30"/>
+      <c r="Z32" s="30"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="30" t="s">
-        <v>430</v>
-      </c>
-      <c r="B33" s="34">
+      <c r="A33" s="31" t="s">
+        <v>431</v>
+      </c>
+      <c r="B33" s="35">
         <v>1.38</v>
       </c>
-      <c r="C33" s="34">
+      <c r="C33" s="35">
         <v>5.13</v>
       </c>
-      <c r="D33" s="34">
+      <c r="D33" s="35">
         <v>2.21</v>
       </c>
-      <c r="E33" s="34">
+      <c r="E33" s="35">
         <v>1.76</v>
       </c>
-      <c r="F33" s="34">
+      <c r="F33" s="35">
         <v>2.07</v>
       </c>
-      <c r="G33" s="34">
+      <c r="G33" s="35">
         <v>2.72</v>
       </c>
-      <c r="H33" s="34">
+      <c r="H33" s="35">
         <v>2.85</v>
       </c>
-      <c r="I33" s="34">
+      <c r="I33" s="35">
         <v>2.14</v>
       </c>
-      <c r="J33" s="34">
+      <c r="J33" s="35">
         <v>1.94</v>
       </c>
-      <c r="K33" s="34">
+      <c r="K33" s="35">
         <v>1.4</v>
       </c>
-      <c r="L33" s="34">
+      <c r="L33" s="35">
         <v>1.4</v>
       </c>
-      <c r="M33" s="34">
+      <c r="M33" s="35">
         <v>1.72</v>
       </c>
-      <c r="N33" s="34">
+      <c r="N33" s="35">
         <v>3.22</v>
       </c>
-      <c r="O33" s="34">
+      <c r="O33" s="35">
         <v>4.19</v>
       </c>
-      <c r="P33" s="34">
+      <c r="P33" s="35">
         <v>0.6</v>
       </c>
-      <c r="Q33" s="34">
+      <c r="Q33" s="35">
         <v>0.0</v>
       </c>
-      <c r="R33" s="34">
+      <c r="R33" s="35">
         <v>11.56</v>
       </c>
-      <c r="S33" s="34">
+      <c r="S33" s="35">
         <v>3.68</v>
       </c>
-      <c r="T33" s="34">
+      <c r="T33" s="35">
         <v>1.87</v>
       </c>
-      <c r="U33" s="34">
+      <c r="U33" s="35">
         <v>6.25</v>
       </c>
-      <c r="V33" s="34">
+      <c r="V33" s="35">
         <v>5.49</v>
       </c>
-      <c r="W33" s="34"/>
-      <c r="X33" s="34"/>
-      <c r="Y33" s="34"/>
-      <c r="Z33" s="34"/>
+      <c r="W33" s="35"/>
+      <c r="X33" s="35"/>
+      <c r="Y33" s="35"/>
+      <c r="Z33" s="35"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="30" t="s">
-        <v>431</v>
-      </c>
-      <c r="B34" s="34">
+      <c r="A34" s="31" t="s">
+        <v>432</v>
+      </c>
+      <c r="B34" s="35">
         <v>2.41</v>
       </c>
-      <c r="C34" s="34">
+      <c r="C34" s="35">
         <v>2.63</v>
       </c>
-      <c r="D34" s="34">
+      <c r="D34" s="35">
         <v>2.25</v>
       </c>
-      <c r="E34" s="34">
+      <c r="E34" s="35">
         <v>2.24</v>
       </c>
-      <c r="F34" s="34">
+      <c r="F34" s="35">
         <v>2.29</v>
       </c>
-      <c r="G34" s="34">
+      <c r="G34" s="35">
         <v>2.13</v>
       </c>
-      <c r="H34" s="34">
+      <c r="H34" s="35">
         <v>1.91</v>
       </c>
-      <c r="I34" s="34">
+      <c r="I34" s="35">
         <v>1.73</v>
       </c>
-      <c r="J34" s="34">
+      <c r="J34" s="35">
         <v>1.79</v>
       </c>
-      <c r="K34" s="34">
+      <c r="K34" s="35">
         <v>1.99</v>
       </c>
-      <c r="L34" s="34">
+      <c r="L34" s="35">
         <v>2.06</v>
       </c>
-      <c r="M34" s="34">
+      <c r="M34" s="35">
         <v>2.01</v>
       </c>
-      <c r="N34" s="34">
+      <c r="N34" s="35">
         <v>2.67</v>
       </c>
-      <c r="O34" s="34">
+      <c r="O34" s="35">
         <v>2.7</v>
       </c>
-      <c r="P34" s="34">
+      <c r="P34" s="35">
         <v>2.09</v>
       </c>
-      <c r="Q34" s="34">
+      <c r="Q34" s="35">
         <v>3.52</v>
       </c>
-      <c r="R34" s="34">
+      <c r="R34" s="35">
         <v>4.67</v>
       </c>
-      <c r="S34" s="34"/>
-      <c r="T34" s="34"/>
-      <c r="U34" s="34"/>
-      <c r="V34" s="34"/>
-      <c r="W34" s="34"/>
-      <c r="X34" s="34"/>
-      <c r="Y34" s="34"/>
-      <c r="Z34" s="34"/>
+      <c r="S34" s="35"/>
+      <c r="T34" s="35"/>
+      <c r="U34" s="35"/>
+      <c r="V34" s="35"/>
+      <c r="W34" s="35"/>
+      <c r="X34" s="35"/>
+      <c r="Y34" s="35"/>
+      <c r="Z34" s="35"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="30" t="s">
-        <v>432</v>
-      </c>
-      <c r="B35" s="34">
+      <c r="A35" s="31" t="s">
+        <v>433</v>
+      </c>
+      <c r="B35" s="35">
         <v>1.97</v>
       </c>
-      <c r="C35" s="34">
+      <c r="C35" s="35">
         <v>7.32</v>
       </c>
-      <c r="D35" s="34">
+      <c r="D35" s="35">
         <v>3.15</v>
       </c>
-      <c r="E35" s="34">
+      <c r="E35" s="35">
         <v>2.52</v>
       </c>
-      <c r="F35" s="34">
+      <c r="F35" s="35">
         <v>2.95</v>
       </c>
-      <c r="G35" s="34">
+      <c r="G35" s="35">
         <v>3.89</v>
       </c>
-      <c r="H35" s="34">
+      <c r="H35" s="35">
         <v>4.08</v>
       </c>
-      <c r="I35" s="34">
+      <c r="I35" s="35">
         <v>3.06</v>
       </c>
-      <c r="J35" s="34">
+      <c r="J35" s="35">
         <v>2.78</v>
       </c>
-      <c r="K35" s="34">
+      <c r="K35" s="35">
         <v>2.0</v>
       </c>
-      <c r="L35" s="34">
+      <c r="L35" s="35">
         <v>2.0</v>
       </c>
-      <c r="M35" s="34">
+      <c r="M35" s="35">
         <v>2.46</v>
       </c>
-      <c r="N35" s="34">
+      <c r="N35" s="35">
         <v>4.6</v>
       </c>
-      <c r="O35" s="34">
+      <c r="O35" s="35">
         <v>5.98</v>
       </c>
-      <c r="P35" s="34">
+      <c r="P35" s="35">
         <v>0.86</v>
       </c>
-      <c r="Q35" s="34">
+      <c r="Q35" s="35">
         <v>0.0</v>
       </c>
-      <c r="R35" s="34">
+      <c r="R35" s="35">
         <v>16.51</v>
       </c>
-      <c r="S35" s="34">
+      <c r="S35" s="35">
         <v>5.26</v>
       </c>
-      <c r="T35" s="34">
+      <c r="T35" s="35">
         <v>2.67</v>
       </c>
-      <c r="U35" s="34">
+      <c r="U35" s="35">
         <v>6.25</v>
       </c>
-      <c r="V35" s="34">
+      <c r="V35" s="35">
         <v>5.49</v>
       </c>
-      <c r="W35" s="34"/>
-      <c r="X35" s="34"/>
-      <c r="Y35" s="34"/>
-      <c r="Z35" s="34"/>
+      <c r="W35" s="35"/>
+      <c r="X35" s="35"/>
+      <c r="Y35" s="35"/>
+      <c r="Z35" s="35"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="30" t="s">
-        <v>433</v>
-      </c>
-      <c r="B36" s="34">
+      <c r="A36" s="31" t="s">
+        <v>434</v>
+      </c>
+      <c r="B36" s="35">
         <v>3.44</v>
       </c>
-      <c r="C36" s="34">
+      <c r="C36" s="35">
         <v>3.75</v>
       </c>
-      <c r="D36" s="34">
+      <c r="D36" s="35">
         <v>3.21</v>
       </c>
-      <c r="E36" s="34">
+      <c r="E36" s="35">
         <v>3.2</v>
       </c>
-      <c r="F36" s="34">
+      <c r="F36" s="35">
         <v>3.27</v>
       </c>
-      <c r="G36" s="34">
+      <c r="G36" s="35">
         <v>3.04</v>
       </c>
-      <c r="H36" s="34">
+      <c r="H36" s="35">
         <v>2.73</v>
       </c>
-      <c r="I36" s="34">
+      <c r="I36" s="35">
         <v>2.47</v>
       </c>
-      <c r="J36" s="34">
+      <c r="J36" s="35">
         <v>2.56</v>
       </c>
-      <c r="K36" s="34">
+      <c r="K36" s="35">
         <v>2.84</v>
       </c>
-      <c r="L36" s="34">
+      <c r="L36" s="35">
         <v>2.95</v>
       </c>
-      <c r="M36" s="34">
+      <c r="M36" s="35">
         <v>2.88</v>
       </c>
-      <c r="N36" s="34">
+      <c r="N36" s="35">
         <v>3.82</v>
       </c>
-      <c r="O36" s="34">
+      <c r="O36" s="35">
         <v>3.86</v>
       </c>
-      <c r="P36" s="34">
+      <c r="P36" s="35">
         <v>2.99</v>
       </c>
-      <c r="Q36" s="34">
+      <c r="Q36" s="35">
         <v>4.31</v>
       </c>
-      <c r="R36" s="34">
+      <c r="R36" s="35">
         <v>5.39</v>
       </c>
-      <c r="S36" s="34"/>
-      <c r="T36" s="34"/>
-      <c r="U36" s="34"/>
-      <c r="V36" s="34"/>
-      <c r="W36" s="34"/>
-      <c r="X36" s="34"/>
-      <c r="Y36" s="34"/>
-      <c r="Z36" s="34"/>
+      <c r="S36" s="35"/>
+      <c r="T36" s="35"/>
+      <c r="U36" s="35"/>
+      <c r="V36" s="35"/>
+      <c r="W36" s="35"/>
+      <c r="X36" s="35"/>
+      <c r="Y36" s="35"/>
+      <c r="Z36" s="35"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="28" t="s">
-        <v>434</v>
-      </c>
-      <c r="B37" s="29"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="29"/>
-      <c r="H37" s="29"/>
-      <c r="I37" s="29"/>
-      <c r="J37" s="29"/>
-      <c r="K37" s="29"/>
-      <c r="L37" s="29"/>
-      <c r="M37" s="29"/>
-      <c r="N37" s="29"/>
-      <c r="O37" s="29"/>
-      <c r="P37" s="29"/>
-      <c r="Q37" s="29"/>
-      <c r="R37" s="29"/>
-      <c r="S37" s="29"/>
-      <c r="T37" s="29"/>
-      <c r="U37" s="29"/>
-      <c r="V37" s="29"/>
-      <c r="W37" s="29"/>
-      <c r="X37" s="29"/>
-      <c r="Y37" s="29"/>
-      <c r="Z37" s="29"/>
+      <c r="A37" s="29" t="s">
+        <v>435</v>
+      </c>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="30"/>
+      <c r="N37" s="30"/>
+      <c r="O37" s="30"/>
+      <c r="P37" s="30"/>
+      <c r="Q37" s="30"/>
+      <c r="R37" s="30"/>
+      <c r="S37" s="30"/>
+      <c r="T37" s="30"/>
+      <c r="U37" s="30"/>
+      <c r="V37" s="30"/>
+      <c r="W37" s="30"/>
+      <c r="X37" s="30"/>
+      <c r="Y37" s="30"/>
+      <c r="Z37" s="30"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="30" t="s">
-        <v>435</v>
-      </c>
-      <c r="B38" s="33">
+      <c r="A38" s="31" t="s">
+        <v>436</v>
+      </c>
+      <c r="B38" s="34">
         <v>0.87</v>
       </c>
-      <c r="C38" s="33">
+      <c r="C38" s="34">
         <v>0.94</v>
       </c>
-      <c r="D38" s="33">
+      <c r="D38" s="34">
         <v>1.08</v>
       </c>
-      <c r="E38" s="33">
+      <c r="E38" s="34">
         <v>1.76</v>
       </c>
-      <c r="F38" s="33">
+      <c r="F38" s="34">
         <v>1.56</v>
       </c>
-      <c r="G38" s="33">
+      <c r="G38" s="34">
         <v>1.18</v>
       </c>
-      <c r="H38" s="33">
+      <c r="H38" s="34">
         <v>1.52</v>
       </c>
-      <c r="I38" s="33">
+      <c r="I38" s="34">
         <v>2.11</v>
       </c>
-      <c r="J38" s="33">
+      <c r="J38" s="34">
         <v>2.43</v>
       </c>
-      <c r="K38" s="33">
+      <c r="K38" s="34">
         <v>2.66</v>
       </c>
-      <c r="L38" s="33">
+      <c r="L38" s="34">
         <v>2.19</v>
       </c>
-      <c r="M38" s="33">
+      <c r="M38" s="34">
         <v>1.7</v>
       </c>
-      <c r="N38" s="33">
+      <c r="N38" s="34">
         <v>1.35</v>
       </c>
-      <c r="O38" s="33">
+      <c r="O38" s="34">
         <v>1.25</v>
       </c>
-      <c r="P38" s="33">
+      <c r="P38" s="34">
         <v>1.3</v>
       </c>
-      <c r="Q38" s="33">
+      <c r="Q38" s="34">
         <v>1.37</v>
       </c>
-      <c r="R38" s="33">
+      <c r="R38" s="34">
         <v>0.41</v>
       </c>
-      <c r="S38" s="33">
+      <c r="S38" s="34">
         <v>1.18</v>
       </c>
-      <c r="T38" s="33">
+      <c r="T38" s="34">
         <v>2.33</v>
       </c>
-      <c r="U38" s="33">
+      <c r="U38" s="34">
         <v>2.11</v>
       </c>
-      <c r="V38" s="33">
+      <c r="V38" s="34">
         <v>1.97</v>
       </c>
-      <c r="W38" s="31"/>
-      <c r="X38" s="31"/>
-      <c r="Y38" s="31"/>
-      <c r="Z38" s="31"/>
+      <c r="W38" s="32"/>
+      <c r="X38" s="32"/>
+      <c r="Y38" s="32"/>
+      <c r="Z38" s="32"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="30" t="s">
-        <v>436</v>
-      </c>
-      <c r="B39" s="33">
+      <c r="A39" s="31" t="s">
+        <v>437</v>
+      </c>
+      <c r="B39" s="34">
         <v>1.2</v>
       </c>
-      <c r="C39" s="33">
+      <c r="C39" s="34">
         <v>1.28</v>
       </c>
-      <c r="D39" s="33">
+      <c r="D39" s="34">
         <v>1.39</v>
       </c>
-      <c r="E39" s="33">
+      <c r="E39" s="34">
         <v>1.6</v>
       </c>
-      <c r="F39" s="33">
+      <c r="F39" s="34">
         <v>1.7</v>
       </c>
-      <c r="G39" s="33">
+      <c r="G39" s="34">
         <v>1.89</v>
       </c>
-      <c r="H39" s="33">
+      <c r="H39" s="34">
         <v>2.16</v>
       </c>
-      <c r="I39" s="33">
+      <c r="I39" s="34">
         <v>2.24</v>
       </c>
-      <c r="J39" s="33">
+      <c r="J39" s="34">
         <v>2.12</v>
       </c>
-      <c r="K39" s="33">
+      <c r="K39" s="34">
         <v>1.9</v>
       </c>
-      <c r="L39" s="33">
+      <c r="L39" s="34">
         <v>1.6</v>
       </c>
-      <c r="M39" s="33">
+      <c r="M39" s="34">
         <v>1.41</v>
       </c>
-      <c r="N39" s="33">
+      <c r="N39" s="34">
         <v>1.17</v>
       </c>
-      <c r="O39" s="33">
+      <c r="O39" s="34">
         <v>1.12</v>
       </c>
-      <c r="P39" s="33">
+      <c r="P39" s="34">
         <v>1.32</v>
       </c>
-      <c r="Q39" s="33">
+      <c r="Q39" s="34">
         <v>1.47</v>
       </c>
-      <c r="R39" s="33">
+      <c r="R39" s="34">
         <v>1.6</v>
       </c>
-      <c r="S39" s="31"/>
-      <c r="T39" s="31"/>
-      <c r="U39" s="31"/>
-      <c r="V39" s="31"/>
-      <c r="W39" s="31"/>
-      <c r="X39" s="31"/>
-      <c r="Y39" s="31"/>
-      <c r="Z39" s="31"/>
+      <c r="S39" s="32"/>
+      <c r="T39" s="32"/>
+      <c r="U39" s="32"/>
+      <c r="V39" s="32"/>
+      <c r="W39" s="32"/>
+      <c r="X39" s="32"/>
+      <c r="Y39" s="32"/>
+      <c r="Z39" s="32"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="28" t="s">
-        <v>437</v>
-      </c>
-      <c r="B40" s="29"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="29"/>
-      <c r="K40" s="29"/>
-      <c r="L40" s="29"/>
-      <c r="M40" s="29"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="29"/>
-      <c r="P40" s="29"/>
-      <c r="Q40" s="29"/>
-      <c r="R40" s="29"/>
-      <c r="S40" s="29"/>
-      <c r="T40" s="29"/>
-      <c r="U40" s="29"/>
-      <c r="V40" s="29"/>
-      <c r="W40" s="29"/>
-      <c r="X40" s="29"/>
-      <c r="Y40" s="29"/>
-      <c r="Z40" s="29"/>
+      <c r="A40" s="29" t="s">
+        <v>438</v>
+      </c>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="30"/>
+      <c r="N40" s="30"/>
+      <c r="O40" s="30"/>
+      <c r="P40" s="30"/>
+      <c r="Q40" s="30"/>
+      <c r="R40" s="30"/>
+      <c r="S40" s="30"/>
+      <c r="T40" s="30"/>
+      <c r="U40" s="30"/>
+      <c r="V40" s="30"/>
+      <c r="W40" s="30"/>
+      <c r="X40" s="30"/>
+      <c r="Y40" s="30"/>
+      <c r="Z40" s="30"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="30" t="s">
-        <v>438</v>
-      </c>
-      <c r="B41" s="33">
+      <c r="A41" s="31" t="s">
+        <v>439</v>
+      </c>
+      <c r="B41" s="34">
         <v>0.95</v>
       </c>
-      <c r="C41" s="33">
+      <c r="C41" s="34">
         <v>1.03</v>
       </c>
-      <c r="D41" s="33">
+      <c r="D41" s="34">
         <v>1.17</v>
       </c>
-      <c r="E41" s="33">
+      <c r="E41" s="34">
         <v>1.95</v>
       </c>
-      <c r="F41" s="33">
+      <c r="F41" s="34">
         <v>1.74</v>
       </c>
-      <c r="G41" s="33">
+      <c r="G41" s="34">
         <v>1.32</v>
       </c>
-      <c r="H41" s="33">
+      <c r="H41" s="34">
         <v>1.79</v>
       </c>
-      <c r="I41" s="33">
+      <c r="I41" s="34">
         <v>2.51</v>
       </c>
-      <c r="J41" s="33">
+      <c r="J41" s="34">
         <v>2.97</v>
       </c>
-      <c r="K41" s="33">
+      <c r="K41" s="34">
         <v>3.3</v>
       </c>
-      <c r="L41" s="33">
+      <c r="L41" s="34">
         <v>2.9</v>
       </c>
-      <c r="M41" s="33">
+      <c r="M41" s="34">
         <v>2.33</v>
       </c>
-      <c r="N41" s="33">
+      <c r="N41" s="34">
         <v>1.89</v>
       </c>
-      <c r="O41" s="33">
+      <c r="O41" s="34">
         <v>1.26</v>
       </c>
-      <c r="P41" s="33">
+      <c r="P41" s="34">
         <v>1.35</v>
       </c>
-      <c r="Q41" s="33">
+      <c r="Q41" s="34">
         <v>1.47</v>
       </c>
-      <c r="R41" s="33">
+      <c r="R41" s="34">
         <v>0.36</v>
       </c>
-      <c r="S41" s="33">
+      <c r="S41" s="34">
         <v>0.96</v>
       </c>
-      <c r="T41" s="33">
+      <c r="T41" s="34">
         <v>1.89</v>
       </c>
-      <c r="U41" s="33">
+      <c r="U41" s="34">
         <v>1.7</v>
       </c>
-      <c r="V41" s="33">
+      <c r="V41" s="34">
         <v>1.58</v>
       </c>
-      <c r="W41" s="31"/>
-      <c r="X41" s="31"/>
-      <c r="Y41" s="31"/>
-      <c r="Z41" s="31"/>
+      <c r="W41" s="32"/>
+      <c r="X41" s="32"/>
+      <c r="Y41" s="32"/>
+      <c r="Z41" s="32"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="30" t="s">
-        <v>439</v>
-      </c>
-      <c r="B42" s="33">
+      <c r="A42" s="31" t="s">
+        <v>440</v>
+      </c>
+      <c r="B42" s="34">
         <v>1.32</v>
       </c>
-      <c r="C42" s="33">
+      <c r="C42" s="34">
         <v>1.41</v>
       </c>
-      <c r="D42" s="33">
+      <c r="D42" s="34">
         <v>1.55</v>
       </c>
-      <c r="E42" s="33">
+      <c r="E42" s="34">
         <v>1.82</v>
       </c>
-      <c r="F42" s="33">
+      <c r="F42" s="34">
         <v>1.96</v>
       </c>
-      <c r="G42" s="33">
+      <c r="G42" s="34">
         <v>2.24</v>
       </c>
-      <c r="H42" s="33">
+      <c r="H42" s="34">
         <v>2.64</v>
       </c>
-      <c r="I42" s="33">
+      <c r="I42" s="34">
         <v>2.82</v>
       </c>
-      <c r="J42" s="33">
+      <c r="J42" s="34">
         <v>2.75</v>
       </c>
-      <c r="K42" s="33">
+      <c r="K42" s="34">
         <v>2.4</v>
       </c>
-      <c r="L42" s="33">
+      <c r="L42" s="34">
         <v>1.96</v>
       </c>
-      <c r="M42" s="33">
+      <c r="M42" s="34">
         <v>1.66</v>
       </c>
-      <c r="N42" s="33">
+      <c r="N42" s="34">
         <v>1.26</v>
       </c>
-      <c r="O42" s="33">
+      <c r="O42" s="34">
         <v>1.08</v>
       </c>
-      <c r="P42" s="33">
+      <c r="P42" s="34">
         <v>1.21</v>
       </c>
-      <c r="Q42" s="33">
+      <c r="Q42" s="34">
         <v>1.28</v>
       </c>
-      <c r="R42" s="33">
+      <c r="R42" s="34">
         <v>1.32</v>
       </c>
-      <c r="S42" s="31"/>
-      <c r="T42" s="31"/>
-      <c r="U42" s="31"/>
-      <c r="V42" s="31"/>
-      <c r="W42" s="31"/>
-      <c r="X42" s="31"/>
-      <c r="Y42" s="31"/>
-      <c r="Z42" s="31"/>
+      <c r="S42" s="32"/>
+      <c r="T42" s="32"/>
+      <c r="U42" s="32"/>
+      <c r="V42" s="32"/>
+      <c r="W42" s="32"/>
+      <c r="X42" s="32"/>
+      <c r="Y42" s="32"/>
+      <c r="Z42" s="32"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="28" t="s">
-        <v>440</v>
-      </c>
-      <c r="B43" s="29"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
-      <c r="G43" s="29"/>
-      <c r="H43" s="29"/>
-      <c r="I43" s="29"/>
-      <c r="J43" s="29"/>
-      <c r="K43" s="29"/>
-      <c r="L43" s="29"/>
-      <c r="M43" s="29"/>
-      <c r="N43" s="29"/>
-      <c r="O43" s="29"/>
-      <c r="P43" s="29"/>
-      <c r="Q43" s="29"/>
-      <c r="R43" s="29"/>
-      <c r="S43" s="29"/>
-      <c r="T43" s="29"/>
-      <c r="U43" s="29"/>
-      <c r="V43" s="29"/>
-      <c r="W43" s="29"/>
-      <c r="X43" s="29"/>
-      <c r="Y43" s="29"/>
-      <c r="Z43" s="29"/>
+      <c r="A43" s="29" t="s">
+        <v>441</v>
+      </c>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="30"/>
+      <c r="M43" s="30"/>
+      <c r="N43" s="30"/>
+      <c r="O43" s="30"/>
+      <c r="P43" s="30"/>
+      <c r="Q43" s="30"/>
+      <c r="R43" s="30"/>
+      <c r="S43" s="30"/>
+      <c r="T43" s="30"/>
+      <c r="U43" s="30"/>
+      <c r="V43" s="30"/>
+      <c r="W43" s="30"/>
+      <c r="X43" s="30"/>
+      <c r="Y43" s="30"/>
+      <c r="Z43" s="30"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="30" t="s">
-        <v>441</v>
-      </c>
-      <c r="B44" s="33">
+      <c r="A44" s="31" t="s">
+        <v>442</v>
+      </c>
+      <c r="B44" s="34">
         <v>0.58</v>
       </c>
-      <c r="C44" s="33">
+      <c r="C44" s="34">
         <v>0.62</v>
       </c>
-      <c r="D44" s="33">
+      <c r="D44" s="34">
         <v>0.68</v>
       </c>
-      <c r="E44" s="33">
+      <c r="E44" s="34">
         <v>1.35</v>
       </c>
-      <c r="F44" s="33">
+      <c r="F44" s="34">
         <v>1.26</v>
       </c>
-      <c r="G44" s="33">
+      <c r="G44" s="34">
         <v>0.94</v>
       </c>
-      <c r="H44" s="33">
+      <c r="H44" s="34">
         <v>0.92</v>
       </c>
-      <c r="I44" s="33">
+      <c r="I44" s="34">
         <v>1.3</v>
       </c>
-      <c r="J44" s="33">
+      <c r="J44" s="34">
         <v>1.46</v>
       </c>
-      <c r="K44" s="33">
+      <c r="K44" s="34">
         <v>1.49</v>
       </c>
-      <c r="L44" s="33">
+      <c r="L44" s="34">
         <v>1.12</v>
       </c>
-      <c r="M44" s="33">
+      <c r="M44" s="34">
         <v>0.85</v>
       </c>
-      <c r="N44" s="33">
+      <c r="N44" s="34">
         <v>0.78</v>
       </c>
-      <c r="O44" s="33">
+      <c r="O44" s="34">
         <v>0.65</v>
       </c>
-      <c r="P44" s="33">
+      <c r="P44" s="34">
         <v>0.68</v>
       </c>
-      <c r="Q44" s="33">
+      <c r="Q44" s="34">
         <v>0.56</v>
       </c>
-      <c r="R44" s="33">
+      <c r="R44" s="34">
         <v>0.14</v>
       </c>
-      <c r="S44" s="33">
+      <c r="S44" s="34">
         <v>0.44</v>
       </c>
-      <c r="T44" s="33">
+      <c r="T44" s="34">
         <v>0.85</v>
       </c>
-      <c r="U44" s="33">
+      <c r="U44" s="34">
         <v>0.78</v>
       </c>
-      <c r="V44" s="33">
+      <c r="V44" s="34">
         <v>0.88</v>
       </c>
-      <c r="W44" s="31"/>
-      <c r="X44" s="31"/>
-      <c r="Y44" s="31"/>
-      <c r="Z44" s="31"/>
+      <c r="W44" s="32"/>
+      <c r="X44" s="32"/>
+      <c r="Y44" s="32"/>
+      <c r="Z44" s="32"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="30" t="s">
-        <v>442</v>
-      </c>
-      <c r="B45" s="33">
+      <c r="A45" s="31" t="s">
+        <v>443</v>
+      </c>
+      <c r="B45" s="34">
         <v>0.83</v>
       </c>
-      <c r="C45" s="33">
+      <c r="C45" s="34">
         <v>0.91</v>
       </c>
-      <c r="D45" s="33">
+      <c r="D45" s="34">
         <v>0.99</v>
       </c>
-      <c r="E45" s="33">
+      <c r="E45" s="34">
         <v>1.16</v>
       </c>
-      <c r="F45" s="33">
+      <c r="F45" s="34">
         <v>1.17</v>
       </c>
-      <c r="G45" s="33">
+      <c r="G45" s="34">
         <v>1.21</v>
       </c>
-      <c r="H45" s="33">
+      <c r="H45" s="34">
         <v>1.26</v>
       </c>
-      <c r="I45" s="33">
+      <c r="I45" s="34">
         <v>1.26</v>
       </c>
-      <c r="J45" s="33">
+      <c r="J45" s="34">
         <v>1.17</v>
       </c>
-      <c r="K45" s="33">
+      <c r="K45" s="34">
         <v>1.01</v>
       </c>
-      <c r="L45" s="33">
+      <c r="L45" s="34">
         <v>0.84</v>
       </c>
-      <c r="M45" s="33">
+      <c r="M45" s="34">
         <v>0.71</v>
       </c>
-      <c r="N45" s="33">
+      <c r="N45" s="34">
         <v>0.55</v>
       </c>
-      <c r="O45" s="33">
+      <c r="O45" s="34">
         <v>0.48</v>
       </c>
-      <c r="P45" s="33">
+      <c r="P45" s="34">
         <v>0.52</v>
       </c>
-      <c r="Q45" s="33">
+      <c r="Q45" s="34">
         <v>0.55</v>
       </c>
-      <c r="R45" s="33">
+      <c r="R45" s="34">
         <v>0.61</v>
       </c>
-      <c r="S45" s="31"/>
-      <c r="T45" s="31"/>
-      <c r="U45" s="31"/>
-      <c r="V45" s="31"/>
-      <c r="W45" s="31"/>
-      <c r="X45" s="31"/>
-      <c r="Y45" s="31"/>
-      <c r="Z45" s="31"/>
+      <c r="S45" s="32"/>
+      <c r="T45" s="32"/>
+      <c r="U45" s="32"/>
+      <c r="V45" s="32"/>
+      <c r="W45" s="32"/>
+      <c r="X45" s="32"/>
+      <c r="Y45" s="32"/>
+      <c r="Z45" s="32"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="28" t="s">
-        <v>443</v>
-      </c>
-      <c r="B46" s="29"/>
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="29"/>
-      <c r="I46" s="29"/>
-      <c r="J46" s="29"/>
-      <c r="K46" s="29"/>
-      <c r="L46" s="29"/>
-      <c r="M46" s="29"/>
-      <c r="N46" s="29"/>
-      <c r="O46" s="29"/>
-      <c r="P46" s="29"/>
-      <c r="Q46" s="29"/>
-      <c r="R46" s="29"/>
-      <c r="S46" s="29"/>
-      <c r="T46" s="29"/>
-      <c r="U46" s="29"/>
-      <c r="V46" s="29"/>
-      <c r="W46" s="29"/>
-      <c r="X46" s="29"/>
-      <c r="Y46" s="29"/>
-      <c r="Z46" s="29"/>
+      <c r="A46" s="29" t="s">
+        <v>444</v>
+      </c>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="30"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
+      <c r="M46" s="30"/>
+      <c r="N46" s="30"/>
+      <c r="O46" s="30"/>
+      <c r="P46" s="30"/>
+      <c r="Q46" s="30"/>
+      <c r="R46" s="30"/>
+      <c r="S46" s="30"/>
+      <c r="T46" s="30"/>
+      <c r="U46" s="30"/>
+      <c r="V46" s="30"/>
+      <c r="W46" s="30"/>
+      <c r="X46" s="30"/>
+      <c r="Y46" s="30"/>
+      <c r="Z46" s="30"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="30" t="s">
-        <v>444</v>
-      </c>
-      <c r="B47" s="33">
+      <c r="A47" s="31" t="s">
+        <v>445</v>
+      </c>
+      <c r="B47" s="34">
         <v>42.52</v>
       </c>
-      <c r="C47" s="32">
+      <c r="C47" s="33">
         <v>225.18</v>
       </c>
-      <c r="D47" s="33">
+      <c r="D47" s="34">
         <v>8.3</v>
       </c>
-      <c r="E47" s="33">
+      <c r="E47" s="34">
         <v>14.92</v>
       </c>
-      <c r="F47" s="33">
+      <c r="F47" s="34">
         <v>27.85</v>
       </c>
-      <c r="G47" s="31"/>
-      <c r="H47" s="31"/>
-      <c r="I47" s="31"/>
-      <c r="J47" s="33">
+      <c r="G47" s="32"/>
+      <c r="H47" s="32"/>
+      <c r="I47" s="32"/>
+      <c r="J47" s="34">
         <v>14.84</v>
       </c>
-      <c r="K47" s="33">
+      <c r="K47" s="34">
         <v>16.38</v>
       </c>
-      <c r="L47" s="33">
+      <c r="L47" s="34">
         <v>13.46</v>
       </c>
-      <c r="M47" s="33">
+      <c r="M47" s="34">
         <v>37.8</v>
       </c>
-      <c r="N47" s="32">
+      <c r="N47" s="33">
         <v>172.23</v>
       </c>
-      <c r="O47" s="33">
+      <c r="O47" s="34">
         <v>7.51</v>
       </c>
-      <c r="P47" s="33">
+      <c r="P47" s="34">
         <v>5.68</v>
       </c>
-      <c r="Q47" s="33">
+      <c r="Q47" s="34">
         <v>7.41</v>
       </c>
-      <c r="R47" s="33">
+      <c r="R47" s="34">
         <v>5.93</v>
       </c>
-      <c r="S47" s="33">
+      <c r="S47" s="34">
         <v>44.49</v>
       </c>
-      <c r="T47" s="33">
+      <c r="T47" s="34">
         <v>41.53</v>
       </c>
-      <c r="U47" s="31"/>
-      <c r="V47" s="33">
+      <c r="U47" s="32"/>
+      <c r="V47" s="34">
         <v>9.78</v>
       </c>
-      <c r="W47" s="31"/>
-      <c r="X47" s="31"/>
-      <c r="Y47" s="31"/>
-      <c r="Z47" s="31"/>
+      <c r="W47" s="32"/>
+      <c r="X47" s="32"/>
+      <c r="Y47" s="32"/>
+      <c r="Z47" s="32"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="30" t="s">
-        <v>445</v>
-      </c>
-      <c r="B48" s="33">
+      <c r="A48" s="31" t="s">
+        <v>446</v>
+      </c>
+      <c r="B48" s="34">
         <v>18.57</v>
       </c>
-      <c r="C48" s="33">
+      <c r="C48" s="34">
         <v>21.76</v>
       </c>
-      <c r="D48" s="33">
+      <c r="D48" s="34">
         <v>37.52</v>
       </c>
-      <c r="E48" s="31"/>
-      <c r="F48" s="31"/>
-      <c r="G48" s="32">
+      <c r="E48" s="32"/>
+      <c r="F48" s="32"/>
+      <c r="G48" s="33">
         <v>1719.17</v>
       </c>
-      <c r="H48" s="33">
+      <c r="H48" s="34">
         <v>58.66</v>
       </c>
-      <c r="I48" s="33">
+      <c r="I48" s="34">
         <v>24.62</v>
       </c>
-      <c r="J48" s="33">
+      <c r="J48" s="34">
         <v>18.36</v>
       </c>
-      <c r="K48" s="33">
+      <c r="K48" s="34">
         <v>17.18</v>
       </c>
-      <c r="L48" s="33">
+      <c r="L48" s="34">
         <v>13.74</v>
       </c>
-      <c r="M48" s="33">
+      <c r="M48" s="34">
         <v>12.24</v>
       </c>
-      <c r="N48" s="33">
+      <c r="N48" s="34">
         <v>9.26</v>
       </c>
-      <c r="O48" s="33">
+      <c r="O48" s="34">
         <v>8.05</v>
       </c>
-      <c r="P48" s="33">
+      <c r="P48" s="34">
         <v>11.24</v>
       </c>
-      <c r="Q48" s="33">
+      <c r="Q48" s="34">
         <v>73.93</v>
       </c>
-      <c r="R48" s="33">
+      <c r="R48" s="34">
         <v>59.85</v>
       </c>
-      <c r="S48" s="31"/>
-      <c r="T48" s="31"/>
-      <c r="U48" s="31"/>
-      <c r="V48" s="31"/>
-      <c r="W48" s="31"/>
-      <c r="X48" s="31"/>
-      <c r="Y48" s="31"/>
-      <c r="Z48" s="31"/>
+      <c r="S48" s="32"/>
+      <c r="T48" s="32"/>
+      <c r="U48" s="32"/>
+      <c r="V48" s="32"/>
+      <c r="W48" s="32"/>
+      <c r="X48" s="32"/>
+      <c r="Y48" s="32"/>
+      <c r="Z48" s="32"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="28" t="s">
-        <v>446</v>
-      </c>
-      <c r="B49" s="29"/>
-      <c r="C49" s="29"/>
-      <c r="D49" s="29"/>
-      <c r="E49" s="29"/>
-      <c r="F49" s="29"/>
-      <c r="G49" s="29"/>
-      <c r="H49" s="29"/>
-      <c r="I49" s="29"/>
-      <c r="J49" s="29"/>
-      <c r="K49" s="29"/>
-      <c r="L49" s="29"/>
-      <c r="M49" s="29"/>
-      <c r="N49" s="29"/>
-      <c r="O49" s="29"/>
-      <c r="P49" s="29"/>
-      <c r="Q49" s="29"/>
-      <c r="R49" s="29"/>
-      <c r="S49" s="29"/>
-      <c r="T49" s="29"/>
-      <c r="U49" s="29"/>
-      <c r="V49" s="29"/>
-      <c r="W49" s="29"/>
-      <c r="X49" s="29"/>
-      <c r="Y49" s="29"/>
-      <c r="Z49" s="29"/>
+      <c r="A49" s="29" t="s">
+        <v>447</v>
+      </c>
+      <c r="B49" s="30"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="30"/>
+      <c r="I49" s="30"/>
+      <c r="J49" s="30"/>
+      <c r="K49" s="30"/>
+      <c r="L49" s="30"/>
+      <c r="M49" s="30"/>
+      <c r="N49" s="30"/>
+      <c r="O49" s="30"/>
+      <c r="P49" s="30"/>
+      <c r="Q49" s="30"/>
+      <c r="R49" s="30"/>
+      <c r="S49" s="30"/>
+      <c r="T49" s="30"/>
+      <c r="U49" s="30"/>
+      <c r="V49" s="30"/>
+      <c r="W49" s="30"/>
+      <c r="X49" s="30"/>
+      <c r="Y49" s="30"/>
+      <c r="Z49" s="30"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="30" t="s">
-        <v>447</v>
-      </c>
-      <c r="B50" s="33">
+      <c r="A50" s="31" t="s">
+        <v>448</v>
+      </c>
+      <c r="B50" s="34">
         <v>5.47</v>
       </c>
-      <c r="C50" s="33">
+      <c r="C50" s="34">
         <v>7.8</v>
       </c>
-      <c r="D50" s="33">
+      <c r="D50" s="34">
         <v>4.11</v>
       </c>
-      <c r="E50" s="33">
+      <c r="E50" s="34">
         <v>10.39</v>
       </c>
-      <c r="F50" s="33">
+      <c r="F50" s="34">
         <v>11.52</v>
       </c>
-      <c r="G50" s="33">
+      <c r="G50" s="34">
         <v>8.31</v>
       </c>
-      <c r="H50" s="33">
+      <c r="H50" s="34">
         <v>8.62</v>
       </c>
-      <c r="I50" s="33">
+      <c r="I50" s="34">
         <v>9.23</v>
       </c>
-      <c r="J50" s="33">
+      <c r="J50" s="34">
         <v>10.71</v>
       </c>
-      <c r="K50" s="33">
+      <c r="K50" s="34">
         <v>9.61</v>
       </c>
-      <c r="L50" s="33">
+      <c r="L50" s="34">
         <v>8.7</v>
       </c>
-      <c r="M50" s="33">
+      <c r="M50" s="34">
         <v>7.92</v>
       </c>
-      <c r="N50" s="33">
+      <c r="N50" s="34">
         <v>5.84</v>
       </c>
-      <c r="O50" s="33">
+      <c r="O50" s="34">
         <v>4.66</v>
       </c>
-      <c r="P50" s="33">
+      <c r="P50" s="34">
         <v>5.29</v>
       </c>
-      <c r="Q50" s="33">
+      <c r="Q50" s="34">
         <v>6.07</v>
       </c>
-      <c r="R50" s="33">
+      <c r="R50" s="34">
         <v>1.66</v>
       </c>
-      <c r="S50" s="33">
+      <c r="S50" s="34">
         <v>4.28</v>
       </c>
-      <c r="T50" s="33">
+      <c r="T50" s="34">
         <v>8.13</v>
       </c>
-      <c r="U50" s="33">
+      <c r="U50" s="34">
         <v>23.63</v>
       </c>
-      <c r="V50" s="33">
+      <c r="V50" s="34">
         <v>7.0</v>
       </c>
-      <c r="W50" s="31"/>
-      <c r="X50" s="31"/>
-      <c r="Y50" s="31"/>
-      <c r="Z50" s="31"/>
+      <c r="W50" s="32"/>
+      <c r="X50" s="32"/>
+      <c r="Y50" s="32"/>
+      <c r="Z50" s="32"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="30" t="s">
-        <v>448</v>
-      </c>
-      <c r="B51" s="33">
+      <c r="A51" s="31" t="s">
+        <v>449</v>
+      </c>
+      <c r="B51" s="34">
         <v>6.97</v>
       </c>
-      <c r="C51" s="33">
+      <c r="C51" s="34">
         <v>7.51</v>
       </c>
-      <c r="D51" s="33">
+      <c r="D51" s="34">
         <v>7.61</v>
       </c>
-      <c r="E51" s="33">
+      <c r="E51" s="34">
         <v>9.64</v>
       </c>
-      <c r="F51" s="33">
+      <c r="F51" s="34">
         <v>9.68</v>
       </c>
-      <c r="G51" s="33">
+      <c r="G51" s="34">
         <v>9.34</v>
       </c>
-      <c r="H51" s="33">
+      <c r="H51" s="34">
         <v>9.41</v>
       </c>
-      <c r="I51" s="33">
+      <c r="I51" s="34">
         <v>9.33</v>
       </c>
-      <c r="J51" s="33">
+      <c r="J51" s="34">
         <v>8.79</v>
       </c>
-      <c r="K51" s="33">
+      <c r="K51" s="34">
         <v>7.64</v>
       </c>
-      <c r="L51" s="33">
+      <c r="L51" s="34">
         <v>6.63</v>
       </c>
-      <c r="M51" s="33">
+      <c r="M51" s="34">
         <v>5.97</v>
       </c>
-      <c r="N51" s="33">
+      <c r="N51" s="34">
         <v>4.8</v>
       </c>
-      <c r="O51" s="33">
+      <c r="O51" s="34">
         <v>4.43</v>
       </c>
-      <c r="P51" s="33">
+      <c r="P51" s="34">
         <v>5.15</v>
       </c>
-      <c r="Q51" s="33">
+      <c r="Q51" s="34">
         <v>6.47</v>
       </c>
-      <c r="R51" s="33">
+      <c r="R51" s="34">
         <v>6.69</v>
       </c>
-      <c r="S51" s="31"/>
-      <c r="T51" s="31"/>
-      <c r="U51" s="31"/>
-      <c r="V51" s="31"/>
-      <c r="W51" s="31"/>
-      <c r="X51" s="31"/>
-      <c r="Y51" s="31"/>
-      <c r="Z51" s="31"/>
+      <c r="S51" s="32"/>
+      <c r="T51" s="32"/>
+      <c r="U51" s="32"/>
+      <c r="V51" s="32"/>
+      <c r="W51" s="32"/>
+      <c r="X51" s="32"/>
+      <c r="Y51" s="32"/>
+      <c r="Z51" s="32"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="28" t="s">
-        <v>449</v>
-      </c>
-      <c r="B52" s="29"/>
-      <c r="C52" s="29"/>
-      <c r="D52" s="29"/>
-      <c r="E52" s="29"/>
-      <c r="F52" s="29"/>
-      <c r="G52" s="29"/>
-      <c r="H52" s="29"/>
-      <c r="I52" s="29"/>
-      <c r="J52" s="29"/>
-      <c r="K52" s="29"/>
-      <c r="L52" s="29"/>
-      <c r="M52" s="29"/>
-      <c r="N52" s="29"/>
-      <c r="O52" s="29"/>
-      <c r="P52" s="29"/>
-      <c r="Q52" s="29"/>
-      <c r="R52" s="29"/>
-      <c r="S52" s="29"/>
-      <c r="T52" s="29"/>
-      <c r="U52" s="29"/>
-      <c r="V52" s="29"/>
-      <c r="W52" s="29"/>
-      <c r="X52" s="29"/>
-      <c r="Y52" s="29"/>
-      <c r="Z52" s="29"/>
+      <c r="A52" s="29" t="s">
+        <v>450</v>
+      </c>
+      <c r="B52" s="30"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
+      <c r="H52" s="30"/>
+      <c r="I52" s="30"/>
+      <c r="J52" s="30"/>
+      <c r="K52" s="30"/>
+      <c r="L52" s="30"/>
+      <c r="M52" s="30"/>
+      <c r="N52" s="30"/>
+      <c r="O52" s="30"/>
+      <c r="P52" s="30"/>
+      <c r="Q52" s="30"/>
+      <c r="R52" s="30"/>
+      <c r="S52" s="30"/>
+      <c r="T52" s="30"/>
+      <c r="U52" s="30"/>
+      <c r="V52" s="30"/>
+      <c r="W52" s="30"/>
+      <c r="X52" s="30"/>
+      <c r="Y52" s="30"/>
+      <c r="Z52" s="30"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="30" t="s">
-        <v>450</v>
-      </c>
-      <c r="B53" s="33">
+      <c r="A53" s="31" t="s">
+        <v>451</v>
+      </c>
+      <c r="B53" s="34">
         <v>14.43</v>
       </c>
-      <c r="C53" s="33">
+      <c r="C53" s="34">
         <v>52.57</v>
       </c>
-      <c r="D53" s="33">
+      <c r="D53" s="34">
         <v>6.33</v>
       </c>
-      <c r="E53" s="33">
+      <c r="E53" s="34">
         <v>23.78</v>
       </c>
-      <c r="F53" s="33">
+      <c r="F53" s="34">
         <v>44.53</v>
       </c>
-      <c r="G53" s="33">
+      <c r="G53" s="34">
         <v>22.65</v>
       </c>
-      <c r="H53" s="33">
+      <c r="H53" s="34">
         <v>21.09</v>
       </c>
-      <c r="I53" s="33">
+      <c r="I53" s="34">
         <v>17.79</v>
       </c>
-      <c r="J53" s="33">
+      <c r="J53" s="34">
         <v>20.87</v>
       </c>
-      <c r="K53" s="33">
+      <c r="K53" s="34">
         <v>17.96</v>
       </c>
-      <c r="L53" s="33">
+      <c r="L53" s="34">
         <v>18.26</v>
       </c>
-      <c r="M53" s="33">
+      <c r="M53" s="34">
         <v>25.07</v>
       </c>
-      <c r="N53" s="33">
+      <c r="N53" s="34">
         <v>11.96</v>
       </c>
-      <c r="O53" s="33">
+      <c r="O53" s="34">
         <v>8.86</v>
       </c>
-      <c r="P53" s="33">
+      <c r="P53" s="34">
         <v>8.53</v>
       </c>
-      <c r="Q53" s="33">
+      <c r="Q53" s="34">
         <v>21.08</v>
       </c>
-      <c r="R53" s="33">
+      <c r="R53" s="34">
         <v>7.18</v>
       </c>
-      <c r="S53" s="33">
+      <c r="S53" s="34">
         <v>5.8</v>
       </c>
-      <c r="T53" s="33">
+      <c r="T53" s="34">
         <v>11.44</v>
       </c>
-      <c r="U53" s="31"/>
-      <c r="V53" s="33">
+      <c r="U53" s="32"/>
+      <c r="V53" s="34">
         <v>7.02</v>
       </c>
-      <c r="W53" s="31"/>
-      <c r="X53" s="31"/>
-      <c r="Y53" s="31"/>
-      <c r="Z53" s="31"/>
+      <c r="W53" s="32"/>
+      <c r="X53" s="32"/>
+      <c r="Y53" s="32"/>
+      <c r="Z53" s="32"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="30" t="s">
-        <v>451</v>
-      </c>
-      <c r="B54" s="33">
+      <c r="A54" s="31" t="s">
+        <v>452</v>
+      </c>
+      <c r="B54" s="34">
         <v>16.12</v>
       </c>
-      <c r="C54" s="33">
+      <c r="C54" s="34">
         <v>17.27</v>
       </c>
-      <c r="D54" s="33">
+      <c r="D54" s="34">
         <v>15.96</v>
       </c>
-      <c r="E54" s="33">
+      <c r="E54" s="34">
         <v>23.84</v>
       </c>
-      <c r="F54" s="33">
+      <c r="F54" s="34">
         <v>23.08</v>
       </c>
-      <c r="G54" s="33">
+      <c r="G54" s="34">
         <v>19.69</v>
       </c>
-      <c r="H54" s="33">
+      <c r="H54" s="34">
         <v>19.03</v>
       </c>
-      <c r="I54" s="33">
+      <c r="I54" s="34">
         <v>19.31</v>
       </c>
-      <c r="J54" s="33">
+      <c r="J54" s="34">
         <v>18.47</v>
       </c>
-      <c r="K54" s="33">
+      <c r="K54" s="34">
         <v>16.06</v>
       </c>
-      <c r="L54" s="33">
+      <c r="L54" s="34">
         <v>13.77</v>
       </c>
-      <c r="M54" s="33">
+      <c r="M54" s="34">
         <v>13.17</v>
       </c>
-      <c r="N54" s="33">
+      <c r="N54" s="34">
         <v>10.7</v>
       </c>
-      <c r="O54" s="33">
+      <c r="O54" s="34">
         <v>8.87</v>
       </c>
-      <c r="P54" s="33">
+      <c r="P54" s="34">
         <v>9.59</v>
       </c>
-      <c r="Q54" s="33">
+      <c r="Q54" s="34">
         <v>15.52</v>
       </c>
-      <c r="R54" s="33">
+      <c r="R54" s="34">
         <v>11.26</v>
       </c>
-      <c r="S54" s="31"/>
-      <c r="T54" s="31"/>
-      <c r="U54" s="31"/>
-      <c r="V54" s="31"/>
-      <c r="W54" s="31"/>
-      <c r="X54" s="31"/>
-      <c r="Y54" s="31"/>
-      <c r="Z54" s="31"/>
+      <c r="S54" s="32"/>
+      <c r="T54" s="32"/>
+      <c r="U54" s="32"/>
+      <c r="V54" s="32"/>
+      <c r="W54" s="32"/>
+      <c r="X54" s="32"/>
+      <c r="Y54" s="32"/>
+      <c r="Z54" s="32"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="28" t="s">
-        <v>452</v>
-      </c>
-      <c r="B55" s="29"/>
-      <c r="C55" s="29"/>
-      <c r="D55" s="29"/>
-      <c r="E55" s="29"/>
-      <c r="F55" s="29"/>
-      <c r="G55" s="29"/>
-      <c r="H55" s="29"/>
-      <c r="I55" s="29"/>
-      <c r="J55" s="29"/>
-      <c r="K55" s="29"/>
-      <c r="L55" s="29"/>
-      <c r="M55" s="29"/>
-      <c r="N55" s="29"/>
-      <c r="O55" s="29"/>
-      <c r="P55" s="29"/>
-      <c r="Q55" s="29"/>
-      <c r="R55" s="29"/>
-      <c r="S55" s="29"/>
-      <c r="T55" s="29"/>
-      <c r="U55" s="29"/>
-      <c r="V55" s="29"/>
-      <c r="W55" s="29"/>
-      <c r="X55" s="29"/>
-      <c r="Y55" s="29"/>
-      <c r="Z55" s="29"/>
+      <c r="A55" s="29" t="s">
+        <v>453</v>
+      </c>
+      <c r="B55" s="30"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="30"/>
+      <c r="I55" s="30"/>
+      <c r="J55" s="30"/>
+      <c r="K55" s="30"/>
+      <c r="L55" s="30"/>
+      <c r="M55" s="30"/>
+      <c r="N55" s="30"/>
+      <c r="O55" s="30"/>
+      <c r="P55" s="30"/>
+      <c r="Q55" s="30"/>
+      <c r="R55" s="30"/>
+      <c r="S55" s="30"/>
+      <c r="T55" s="30"/>
+      <c r="U55" s="30"/>
+      <c r="V55" s="30"/>
+      <c r="W55" s="30"/>
+      <c r="X55" s="30"/>
+      <c r="Y55" s="30"/>
+      <c r="Z55" s="30"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="30" t="s">
-        <v>453</v>
-      </c>
-      <c r="B56" s="33">
+      <c r="A56" s="31" t="s">
+        <v>454</v>
+      </c>
+      <c r="B56" s="34">
         <v>16.99</v>
       </c>
-      <c r="C56" s="33">
+      <c r="C56" s="34">
         <v>32.41</v>
       </c>
-      <c r="D56" s="33">
+      <c r="D56" s="34">
         <v>6.38</v>
       </c>
-      <c r="E56" s="33">
+      <c r="E56" s="34">
         <v>20.26</v>
       </c>
-      <c r="F56" s="33">
+      <c r="F56" s="34">
         <v>51.9</v>
       </c>
-      <c r="G56" s="33">
+      <c r="G56" s="34">
         <v>22.63</v>
       </c>
-      <c r="H56" s="33">
+      <c r="H56" s="34">
         <v>13.33</v>
       </c>
-      <c r="I56" s="33">
+      <c r="I56" s="34">
         <v>16.18</v>
       </c>
-      <c r="J56" s="33">
+      <c r="J56" s="34">
         <v>20.87</v>
       </c>
-      <c r="K56" s="33">
+      <c r="K56" s="34">
         <v>17.96</v>
       </c>
-      <c r="L56" s="33">
+      <c r="L56" s="34">
         <v>18.26</v>
       </c>
-      <c r="M56" s="33">
+      <c r="M56" s="34">
         <v>25.07</v>
       </c>
-      <c r="N56" s="33">
+      <c r="N56" s="34">
         <v>11.96</v>
       </c>
-      <c r="O56" s="33">
+      <c r="O56" s="34">
         <v>8.73</v>
       </c>
-      <c r="P56" s="33">
+      <c r="P56" s="34">
         <v>11.12</v>
       </c>
-      <c r="Q56" s="33">
+      <c r="Q56" s="34">
         <v>28.62</v>
       </c>
-      <c r="R56" s="33">
+      <c r="R56" s="34">
         <v>7.33</v>
       </c>
-      <c r="S56" s="33">
+      <c r="S56" s="34">
         <v>10.44</v>
       </c>
-      <c r="T56" s="33">
+      <c r="T56" s="34">
         <v>20.56</v>
       </c>
-      <c r="U56" s="31"/>
-      <c r="V56" s="33">
+      <c r="U56" s="32"/>
+      <c r="V56" s="34">
         <v>12.61</v>
       </c>
-      <c r="W56" s="31"/>
-      <c r="X56" s="31"/>
-      <c r="Y56" s="31"/>
-      <c r="Z56" s="31"/>
+      <c r="W56" s="32"/>
+      <c r="X56" s="32"/>
+      <c r="Y56" s="32"/>
+      <c r="Z56" s="32"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="30" t="s">
-        <v>454</v>
-      </c>
-      <c r="B57" s="33">
+      <c r="A57" s="31" t="s">
+        <v>455</v>
+      </c>
+      <c r="B57" s="34">
         <v>1.2</v>
       </c>
-      <c r="C57" s="33">
+      <c r="C57" s="34">
         <v>1.28</v>
       </c>
-      <c r="D57" s="33">
+      <c r="D57" s="34">
         <v>1.39</v>
       </c>
-      <c r="E57" s="33">
+      <c r="E57" s="34">
         <v>1.6</v>
       </c>
-      <c r="F57" s="33">
+      <c r="F57" s="34">
         <v>1.7</v>
       </c>
-      <c r="G57" s="33">
+      <c r="G57" s="34">
         <v>1.89</v>
       </c>
-      <c r="H57" s="33">
+      <c r="H57" s="34">
         <v>2.16</v>
       </c>
-      <c r="I57" s="33">
+      <c r="I57" s="34">
         <v>2.24</v>
       </c>
-      <c r="J57" s="33">
+      <c r="J57" s="34">
         <v>2.12</v>
       </c>
-      <c r="K57" s="33">
+      <c r="K57" s="34">
         <v>1.9</v>
       </c>
-      <c r="L57" s="33">
+      <c r="L57" s="34">
         <v>1.6</v>
       </c>
-      <c r="M57" s="33">
+      <c r="M57" s="34">
         <v>1.41</v>
       </c>
-      <c r="N57" s="33">
+      <c r="N57" s="34">
         <v>1.13</v>
       </c>
-      <c r="O57" s="33">
+      <c r="O57" s="34">
         <v>1.03</v>
       </c>
-      <c r="P57" s="33">
+      <c r="P57" s="34">
         <v>1.16</v>
       </c>
-      <c r="Q57" s="33">
+      <c r="Q57" s="34">
         <v>1.24</v>
       </c>
-      <c r="R57" s="33">
+      <c r="R57" s="34">
         <v>1.29</v>
       </c>
-      <c r="S57" s="31"/>
-      <c r="T57" s="31"/>
-      <c r="U57" s="31"/>
-      <c r="V57" s="31"/>
-      <c r="W57" s="31"/>
-      <c r="X57" s="31"/>
-      <c r="Y57" s="31"/>
-      <c r="Z57" s="31"/>
+      <c r="S57" s="32"/>
+      <c r="T57" s="32"/>
+      <c r="U57" s="32"/>
+      <c r="V57" s="32"/>
+      <c r="W57" s="32"/>
+      <c r="X57" s="32"/>
+      <c r="Y57" s="32"/>
+      <c r="Z57" s="32"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="28" t="s">
-        <v>455</v>
-      </c>
-      <c r="B58" s="29"/>
-      <c r="C58" s="29"/>
-      <c r="D58" s="29"/>
-      <c r="E58" s="29"/>
-      <c r="F58" s="29"/>
-      <c r="G58" s="29"/>
-      <c r="H58" s="29"/>
-      <c r="I58" s="29"/>
-      <c r="J58" s="29"/>
-      <c r="K58" s="29"/>
-      <c r="L58" s="29"/>
-      <c r="M58" s="29"/>
-      <c r="N58" s="29"/>
-      <c r="O58" s="29"/>
-      <c r="P58" s="29"/>
-      <c r="Q58" s="29"/>
-      <c r="R58" s="29"/>
-      <c r="S58" s="29"/>
-      <c r="T58" s="29"/>
-      <c r="U58" s="29"/>
-      <c r="V58" s="29"/>
-      <c r="W58" s="29"/>
-      <c r="X58" s="29"/>
-      <c r="Y58" s="29"/>
-      <c r="Z58" s="29"/>
+      <c r="A58" s="29" t="s">
+        <v>456</v>
+      </c>
+      <c r="B58" s="30"/>
+      <c r="C58" s="30"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="30"/>
+      <c r="H58" s="30"/>
+      <c r="I58" s="30"/>
+      <c r="J58" s="30"/>
+      <c r="K58" s="30"/>
+      <c r="L58" s="30"/>
+      <c r="M58" s="30"/>
+      <c r="N58" s="30"/>
+      <c r="O58" s="30"/>
+      <c r="P58" s="30"/>
+      <c r="Q58" s="30"/>
+      <c r="R58" s="30"/>
+      <c r="S58" s="30"/>
+      <c r="T58" s="30"/>
+      <c r="U58" s="30"/>
+      <c r="V58" s="30"/>
+      <c r="W58" s="30"/>
+      <c r="X58" s="30"/>
+      <c r="Y58" s="30"/>
+      <c r="Z58" s="30"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="30" t="s">
-        <v>456</v>
-      </c>
-      <c r="B59" s="33">
+      <c r="A59" s="31" t="s">
+        <v>457</v>
+      </c>
+      <c r="B59" s="34">
         <v>0.06</v>
       </c>
-      <c r="C59" s="36">
+      <c r="C59" s="37">
         <v>-0.58</v>
       </c>
-      <c r="D59" s="33">
+      <c r="D59" s="34">
         <v>0.03</v>
       </c>
-      <c r="E59" s="33">
+      <c r="E59" s="34">
         <v>0.2</v>
       </c>
-      <c r="F59" s="36">
+      <c r="F59" s="37">
         <v>-1.35</v>
       </c>
-      <c r="G59" s="36">
+      <c r="G59" s="37">
         <v>-9.58</v>
       </c>
-      <c r="H59" s="36">
+      <c r="H59" s="37">
         <v>-0.58</v>
       </c>
-      <c r="I59" s="33">
+      <c r="I59" s="34">
         <v>2.31</v>
       </c>
-      <c r="J59" s="36">
+      <c r="J59" s="37">
         <v>-1.28</v>
       </c>
-      <c r="K59" s="33">
+      <c r="K59" s="34">
         <v>0.43</v>
       </c>
-      <c r="L59" s="33">
+      <c r="L59" s="34">
         <v>0.2</v>
       </c>
-      <c r="M59" s="36">
+      <c r="M59" s="37">
         <v>-0.68</v>
       </c>
-      <c r="N59" s="36">
+      <c r="N59" s="37">
         <v>-3.3</v>
       </c>
-      <c r="O59" s="36">
+      <c r="O59" s="37">
         <v>-2.71</v>
       </c>
-      <c r="P59" s="33">
+      <c r="P59" s="34">
         <v>0.05</v>
       </c>
-      <c r="Q59" s="33">
+      <c r="Q59" s="34">
         <v>1.01</v>
       </c>
-      <c r="R59" s="36">
+      <c r="R59" s="37">
         <v>-0.1</v>
       </c>
-      <c r="S59" s="33">
+      <c r="S59" s="34">
         <v>0.73</v>
       </c>
-      <c r="T59" s="33">
+      <c r="T59" s="34">
         <v>0.03</v>
       </c>
-      <c r="U59" s="31"/>
-      <c r="V59" s="36">
+      <c r="U59" s="32"/>
+      <c r="V59" s="37">
         <v>-0.27</v>
       </c>
-      <c r="W59" s="31"/>
-      <c r="X59" s="31"/>
-      <c r="Y59" s="31"/>
-      <c r="Z59" s="31"/>
+      <c r="W59" s="32"/>
+      <c r="X59" s="32"/>
+      <c r="Y59" s="32"/>
+      <c r="Z59" s="32"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="30" t="s">
-        <v>457</v>
-      </c>
-      <c r="B60" s="33">
+      <c r="A60" s="31" t="s">
+        <v>458</v>
+      </c>
+      <c r="B60" s="34">
         <v>1.78</v>
       </c>
-      <c r="C60" s="36">
+      <c r="C60" s="37">
         <v>-1.08</v>
       </c>
-      <c r="D60" s="33">
+      <c r="D60" s="34">
         <v>0.72</v>
       </c>
-      <c r="E60" s="36">
+      <c r="E60" s="37">
         <v>-56.57</v>
       </c>
-      <c r="F60" s="36">
+      <c r="F60" s="37">
         <v>-1.29</v>
       </c>
-      <c r="G60" s="36">
+      <c r="G60" s="37">
         <v>-4.34</v>
       </c>
-      <c r="H60" s="33">
+      <c r="H60" s="34">
         <v>2.1</v>
       </c>
-      <c r="I60" s="33">
+      <c r="I60" s="34">
         <v>2.14</v>
       </c>
-      <c r="J60" s="33">
+      <c r="J60" s="34">
         <v>2.78</v>
       </c>
-      <c r="K60" s="33">
+      <c r="K60" s="34">
         <v>1.65</v>
       </c>
-      <c r="L60" s="33">
+      <c r="L60" s="34">
         <v>0.55</v>
       </c>
-      <c r="M60" s="33">
+      <c r="M60" s="34">
         <v>0.94</v>
       </c>
-      <c r="N60" s="36">
+      <c r="N60" s="37">
         <v>-2.27</v>
       </c>
-      <c r="O60" s="36">
+      <c r="O60" s="37">
         <v>-3.49</v>
       </c>
-      <c r="P60" s="31"/>
-      <c r="Q60" s="36">
+      <c r="P60" s="32"/>
+      <c r="Q60" s="37">
         <v>-0.58</v>
       </c>
-      <c r="R60" s="36">
+      <c r="R60" s="37">
         <v>-0.33</v>
       </c>
-      <c r="S60" s="31"/>
-      <c r="T60" s="31"/>
-      <c r="U60" s="31"/>
-      <c r="V60" s="31"/>
-      <c r="W60" s="31"/>
-      <c r="X60" s="31"/>
-      <c r="Y60" s="31"/>
-      <c r="Z60" s="31"/>
+      <c r="S60" s="32"/>
+      <c r="T60" s="32"/>
+      <c r="U60" s="32"/>
+      <c r="V60" s="32"/>
+      <c r="W60" s="32"/>
+      <c r="X60" s="32"/>
+      <c r="Y60" s="32"/>
+      <c r="Z60" s="32"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="28" t="s">
-        <v>458</v>
-      </c>
-      <c r="B61" s="29"/>
-      <c r="C61" s="29"/>
-      <c r="D61" s="29"/>
-      <c r="E61" s="29"/>
-      <c r="F61" s="29"/>
-      <c r="G61" s="29"/>
-      <c r="H61" s="29"/>
-      <c r="I61" s="29"/>
-      <c r="J61" s="29"/>
-      <c r="K61" s="29"/>
-      <c r="L61" s="29"/>
-      <c r="M61" s="29"/>
-      <c r="N61" s="29"/>
-      <c r="O61" s="29"/>
-      <c r="P61" s="29"/>
-      <c r="Q61" s="29"/>
-      <c r="R61" s="29"/>
-      <c r="S61" s="29"/>
-      <c r="T61" s="29"/>
-      <c r="U61" s="29"/>
-      <c r="V61" s="29"/>
-      <c r="W61" s="29"/>
-      <c r="X61" s="29"/>
-      <c r="Y61" s="29"/>
-      <c r="Z61" s="29"/>
+      <c r="A61" s="29" t="s">
+        <v>459</v>
+      </c>
+      <c r="B61" s="30"/>
+      <c r="C61" s="30"/>
+      <c r="D61" s="30"/>
+      <c r="E61" s="30"/>
+      <c r="F61" s="30"/>
+      <c r="G61" s="30"/>
+      <c r="H61" s="30"/>
+      <c r="I61" s="30"/>
+      <c r="J61" s="30"/>
+      <c r="K61" s="30"/>
+      <c r="L61" s="30"/>
+      <c r="M61" s="30"/>
+      <c r="N61" s="30"/>
+      <c r="O61" s="30"/>
+      <c r="P61" s="30"/>
+      <c r="Q61" s="30"/>
+      <c r="R61" s="30"/>
+      <c r="S61" s="30"/>
+      <c r="T61" s="30"/>
+      <c r="U61" s="30"/>
+      <c r="V61" s="30"/>
+      <c r="W61" s="30"/>
+      <c r="X61" s="30"/>
+      <c r="Y61" s="30"/>
+      <c r="Z61" s="30"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="30" t="s">
-        <v>459</v>
-      </c>
-      <c r="B62" s="33">
+      <c r="A62" s="31" t="s">
+        <v>460</v>
+      </c>
+      <c r="B62" s="34">
         <v>0.71</v>
       </c>
-      <c r="C62" s="33">
+      <c r="C62" s="34">
         <v>0.75</v>
       </c>
-      <c r="D62" s="33">
+      <c r="D62" s="34">
         <v>0.82</v>
       </c>
-      <c r="E62" s="33">
+      <c r="E62" s="34">
         <v>1.48</v>
       </c>
-      <c r="F62" s="33">
+      <c r="F62" s="34">
         <v>1.46</v>
       </c>
-      <c r="G62" s="33">
+      <c r="G62" s="34">
         <v>1.13</v>
       </c>
-      <c r="H62" s="33">
+      <c r="H62" s="34">
         <v>1.29</v>
       </c>
-      <c r="I62" s="33">
+      <c r="I62" s="34">
         <v>1.53</v>
       </c>
-      <c r="J62" s="33">
+      <c r="J62" s="34">
         <v>1.62</v>
       </c>
-      <c r="K62" s="33">
+      <c r="K62" s="34">
         <v>1.7</v>
       </c>
-      <c r="L62" s="33">
+      <c r="L62" s="34">
         <v>1.43</v>
       </c>
-      <c r="M62" s="33">
+      <c r="M62" s="34">
         <v>1.25</v>
       </c>
-      <c r="N62" s="33">
+      <c r="N62" s="34">
         <v>1.93</v>
       </c>
-      <c r="O62" s="33">
+      <c r="O62" s="34">
         <v>0.64</v>
       </c>
-      <c r="P62" s="33">
+      <c r="P62" s="34">
         <v>0.72</v>
       </c>
-      <c r="Q62" s="33">
+      <c r="Q62" s="34">
         <v>0.86</v>
       </c>
-      <c r="R62" s="33">
+      <c r="R62" s="34">
         <v>0.46</v>
       </c>
-      <c r="S62" s="33">
+      <c r="S62" s="34">
         <v>0.77</v>
       </c>
-      <c r="T62" s="33">
+      <c r="T62" s="34">
         <v>1.2</v>
       </c>
-      <c r="U62" s="33">
+      <c r="U62" s="34">
         <v>1.16</v>
       </c>
-      <c r="V62" s="33">
+      <c r="V62" s="34">
         <v>1.07</v>
       </c>
-      <c r="W62" s="33">
+      <c r="W62" s="34">
         <v>1.06</v>
       </c>
-      <c r="X62" s="33">
+      <c r="X62" s="34">
         <v>1.03</v>
       </c>
-      <c r="Y62" s="33">
+      <c r="Y62" s="34">
         <v>0.88</v>
       </c>
-      <c r="Z62" s="31"/>
+      <c r="Z62" s="32"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="30" t="s">
-        <v>460</v>
-      </c>
-      <c r="B63" s="33">
+      <c r="A63" s="31" t="s">
+        <v>461</v>
+      </c>
+      <c r="B63" s="34">
         <v>0.96</v>
       </c>
-      <c r="C63" s="33">
+      <c r="C63" s="34">
         <v>1.06</v>
       </c>
-      <c r="D63" s="33">
+      <c r="D63" s="34">
         <v>1.19</v>
       </c>
-      <c r="E63" s="33">
+      <c r="E63" s="34">
         <v>1.38</v>
       </c>
-      <c r="F63" s="33">
+      <c r="F63" s="34">
         <v>1.4</v>
       </c>
-      <c r="G63" s="33">
+      <c r="G63" s="34">
         <v>1.44</v>
       </c>
-      <c r="H63" s="33">
+      <c r="H63" s="34">
         <v>1.51</v>
       </c>
-      <c r="I63" s="33">
+      <c r="I63" s="34">
         <v>1.51</v>
       </c>
-      <c r="J63" s="33">
+      <c r="J63" s="34">
         <v>1.55</v>
       </c>
-      <c r="K63" s="33">
+      <c r="K63" s="34">
         <v>1.43</v>
       </c>
-      <c r="L63" s="33">
+      <c r="L63" s="34">
         <v>1.26</v>
       </c>
-      <c r="M63" s="33">
+      <c r="M63" s="34">
         <v>1.14</v>
       </c>
-      <c r="N63" s="33">
+      <c r="N63" s="34">
         <v>0.97</v>
       </c>
-      <c r="O63" s="33">
+      <c r="O63" s="34">
         <v>0.69</v>
       </c>
-      <c r="P63" s="33">
+      <c r="P63" s="34">
         <v>0.79</v>
       </c>
-      <c r="Q63" s="33">
+      <c r="Q63" s="34">
         <v>0.88</v>
       </c>
-      <c r="R63" s="33">
+      <c r="R63" s="34">
         <v>0.92</v>
       </c>
-      <c r="S63" s="33">
+      <c r="S63" s="34">
         <v>1.05</v>
       </c>
-      <c r="T63" s="33">
+      <c r="T63" s="34">
         <v>1.1</v>
       </c>
-      <c r="U63" s="33">
+      <c r="U63" s="34">
         <v>1.04</v>
       </c>
-      <c r="V63" s="31"/>
-      <c r="W63" s="31"/>
-      <c r="X63" s="31"/>
-      <c r="Y63" s="31"/>
-      <c r="Z63" s="31"/>
+      <c r="V63" s="32"/>
+      <c r="W63" s="32"/>
+      <c r="X63" s="32"/>
+      <c r="Y63" s="32"/>
+      <c r="Z63" s="32"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="28" t="s">
-        <v>461</v>
-      </c>
-      <c r="B64" s="29"/>
-      <c r="C64" s="29"/>
-      <c r="D64" s="29"/>
-      <c r="E64" s="29"/>
-      <c r="F64" s="29"/>
-      <c r="G64" s="29"/>
-      <c r="H64" s="29"/>
-      <c r="I64" s="29"/>
-      <c r="J64" s="29"/>
-      <c r="K64" s="29"/>
-      <c r="L64" s="29"/>
-      <c r="M64" s="29"/>
-      <c r="N64" s="29"/>
-      <c r="O64" s="29"/>
-      <c r="P64" s="29"/>
-      <c r="Q64" s="29"/>
-      <c r="R64" s="29"/>
-      <c r="S64" s="29"/>
-      <c r="T64" s="29"/>
-      <c r="U64" s="29"/>
-      <c r="V64" s="29"/>
-      <c r="W64" s="29"/>
-      <c r="X64" s="29"/>
-      <c r="Y64" s="29"/>
-      <c r="Z64" s="29"/>
+      <c r="A64" s="29" t="s">
+        <v>462</v>
+      </c>
+      <c r="B64" s="30"/>
+      <c r="C64" s="30"/>
+      <c r="D64" s="30"/>
+      <c r="E64" s="30"/>
+      <c r="F64" s="30"/>
+      <c r="G64" s="30"/>
+      <c r="H64" s="30"/>
+      <c r="I64" s="30"/>
+      <c r="J64" s="30"/>
+      <c r="K64" s="30"/>
+      <c r="L64" s="30"/>
+      <c r="M64" s="30"/>
+      <c r="N64" s="30"/>
+      <c r="O64" s="30"/>
+      <c r="P64" s="30"/>
+      <c r="Q64" s="30"/>
+      <c r="R64" s="30"/>
+      <c r="S64" s="30"/>
+      <c r="T64" s="30"/>
+      <c r="U64" s="30"/>
+      <c r="V64" s="30"/>
+      <c r="W64" s="30"/>
+      <c r="X64" s="30"/>
+      <c r="Y64" s="30"/>
+      <c r="Z64" s="30"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="30" t="s">
-        <v>462</v>
-      </c>
-      <c r="B65" s="33">
+      <c r="A65" s="31" t="s">
+        <v>463</v>
+      </c>
+      <c r="B65" s="34">
         <v>6.08</v>
       </c>
-      <c r="C65" s="33">
+      <c r="C65" s="34">
         <v>8.1</v>
       </c>
-      <c r="D65" s="33">
+      <c r="D65" s="34">
         <v>4.31</v>
       </c>
-      <c r="E65" s="33">
+      <c r="E65" s="34">
         <v>9.51</v>
       </c>
-      <c r="F65" s="33">
+      <c r="F65" s="34">
         <v>13.79</v>
       </c>
-      <c r="G65" s="33">
+      <c r="G65" s="34">
         <v>9.71</v>
       </c>
-      <c r="H65" s="33">
+      <c r="H65" s="34">
         <v>8.67</v>
       </c>
-      <c r="I65" s="33">
+      <c r="I65" s="34">
         <v>8.74</v>
       </c>
-      <c r="J65" s="33">
+      <c r="J65" s="34">
         <v>10.03</v>
       </c>
-      <c r="K65" s="33">
+      <c r="K65" s="34">
         <v>9.26</v>
       </c>
-      <c r="L65" s="33">
+      <c r="L65" s="34">
         <v>9.11</v>
       </c>
-      <c r="M65" s="33">
+      <c r="M65" s="34">
         <v>9.56</v>
       </c>
-      <c r="N65" s="33">
+      <c r="N65" s="34">
         <v>16.85</v>
       </c>
-      <c r="O65" s="33">
+      <c r="O65" s="34">
         <v>3.76</v>
       </c>
-      <c r="P65" s="33">
+      <c r="P65" s="34">
         <v>3.83</v>
       </c>
-      <c r="Q65" s="33">
+      <c r="Q65" s="34">
         <v>7.7</v>
       </c>
-      <c r="R65" s="33">
+      <c r="R65" s="34">
         <v>4.47</v>
       </c>
-      <c r="S65" s="33">
+      <c r="S65" s="34">
         <v>5.62</v>
       </c>
-      <c r="T65" s="33">
+      <c r="T65" s="34">
         <v>8.66</v>
       </c>
-      <c r="U65" s="33">
+      <c r="U65" s="34">
         <v>37.03</v>
       </c>
-      <c r="V65" s="33">
+      <c r="V65" s="34">
         <v>6.49</v>
       </c>
-      <c r="W65" s="33">
+      <c r="W65" s="34">
         <v>4.94</v>
       </c>
-      <c r="X65" s="33">
+      <c r="X65" s="34">
         <v>4.62</v>
       </c>
-      <c r="Y65" s="33">
+      <c r="Y65" s="34">
         <v>3.72</v>
       </c>
-      <c r="Z65" s="31"/>
+      <c r="Z65" s="32"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="30" t="s">
-        <v>463</v>
-      </c>
-      <c r="B66" s="33">
+      <c r="A66" s="31" t="s">
+        <v>464</v>
+      </c>
+      <c r="B66" s="34">
         <v>7.21</v>
       </c>
-      <c r="C66" s="33">
+      <c r="C66" s="34">
         <v>7.81</v>
       </c>
-      <c r="D66" s="33">
+      <c r="D66" s="34">
         <v>7.9</v>
       </c>
-      <c r="E66" s="33">
+      <c r="E66" s="34">
         <v>9.83</v>
       </c>
-      <c r="F66" s="33">
+      <c r="F66" s="34">
         <v>9.95</v>
       </c>
-      <c r="G66" s="33">
+      <c r="G66" s="34">
         <v>9.25</v>
       </c>
-      <c r="H66" s="33">
+      <c r="H66" s="34">
         <v>9.15</v>
       </c>
-      <c r="I66" s="33">
+      <c r="I66" s="34">
         <v>9.31</v>
       </c>
-      <c r="J66" s="33">
+      <c r="J66" s="34">
         <v>10.09</v>
       </c>
-      <c r="K66" s="33">
+      <c r="K66" s="34">
         <v>9.3</v>
       </c>
-      <c r="L66" s="33">
+      <c r="L66" s="34">
         <v>8.45</v>
       </c>
-      <c r="M66" s="33">
+      <c r="M66" s="34">
         <v>8.09</v>
       </c>
-      <c r="N66" s="33">
+      <c r="N66" s="34">
         <v>7.0</v>
       </c>
-      <c r="O66" s="33">
+      <c r="O66" s="34">
         <v>4.78</v>
       </c>
-      <c r="P66" s="33">
+      <c r="P66" s="34">
         <v>5.81</v>
       </c>
-      <c r="Q66" s="33">
+      <c r="Q66" s="34">
         <v>8.32</v>
       </c>
-      <c r="R66" s="33">
+      <c r="R66" s="34">
         <v>7.94</v>
       </c>
-      <c r="S66" s="33">
+      <c r="S66" s="34">
         <v>7.59</v>
       </c>
-      <c r="T66" s="33">
+      <c r="T66" s="34">
         <v>7.12</v>
       </c>
-      <c r="U66" s="33">
+      <c r="U66" s="34">
         <v>5.94</v>
       </c>
-      <c r="V66" s="31"/>
-      <c r="W66" s="31"/>
-      <c r="X66" s="31"/>
-      <c r="Y66" s="31"/>
-      <c r="Z66" s="31"/>
+      <c r="V66" s="32"/>
+      <c r="W66" s="32"/>
+      <c r="X66" s="32"/>
+      <c r="Y66" s="32"/>
+      <c r="Z66" s="32"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="28" t="s">
-        <v>464</v>
-      </c>
-      <c r="B67" s="29"/>
-      <c r="C67" s="29"/>
-      <c r="D67" s="29"/>
-      <c r="E67" s="29"/>
-      <c r="F67" s="29"/>
-      <c r="G67" s="29"/>
-      <c r="H67" s="29"/>
-      <c r="I67" s="29"/>
-      <c r="J67" s="29"/>
-      <c r="K67" s="29"/>
-      <c r="L67" s="29"/>
-      <c r="M67" s="29"/>
-      <c r="N67" s="29"/>
-      <c r="O67" s="29"/>
-      <c r="P67" s="29"/>
-      <c r="Q67" s="29"/>
-      <c r="R67" s="29"/>
-      <c r="S67" s="29"/>
-      <c r="T67" s="29"/>
-      <c r="U67" s="29"/>
-      <c r="V67" s="29"/>
-      <c r="W67" s="29"/>
-      <c r="X67" s="29"/>
-      <c r="Y67" s="29"/>
-      <c r="Z67" s="29"/>
+      <c r="A67" s="29" t="s">
+        <v>465</v>
+      </c>
+      <c r="B67" s="30"/>
+      <c r="C67" s="30"/>
+      <c r="D67" s="30"/>
+      <c r="E67" s="30"/>
+      <c r="F67" s="30"/>
+      <c r="G67" s="30"/>
+      <c r="H67" s="30"/>
+      <c r="I67" s="30"/>
+      <c r="J67" s="30"/>
+      <c r="K67" s="30"/>
+      <c r="L67" s="30"/>
+      <c r="M67" s="30"/>
+      <c r="N67" s="30"/>
+      <c r="O67" s="30"/>
+      <c r="P67" s="30"/>
+      <c r="Q67" s="30"/>
+      <c r="R67" s="30"/>
+      <c r="S67" s="30"/>
+      <c r="T67" s="30"/>
+      <c r="U67" s="30"/>
+      <c r="V67" s="30"/>
+      <c r="W67" s="30"/>
+      <c r="X67" s="30"/>
+      <c r="Y67" s="30"/>
+      <c r="Z67" s="30"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="30" t="s">
-        <v>465</v>
-      </c>
-      <c r="B68" s="33">
+      <c r="A68" s="31" t="s">
+        <v>466</v>
+      </c>
+      <c r="B68" s="34">
         <v>10.14</v>
       </c>
-      <c r="C68" s="33">
+      <c r="C68" s="34">
         <v>9.37</v>
       </c>
-      <c r="D68" s="33">
+      <c r="D68" s="34">
         <v>5.14</v>
       </c>
-      <c r="E68" s="33">
+      <c r="E68" s="34">
         <v>9.95</v>
       </c>
-      <c r="F68" s="33">
+      <c r="F68" s="34">
         <v>14.95</v>
       </c>
-      <c r="G68" s="33">
+      <c r="G68" s="34">
         <v>11.93</v>
       </c>
-      <c r="H68" s="33">
+      <c r="H68" s="34">
         <v>12.2</v>
       </c>
-      <c r="I68" s="33">
+      <c r="I68" s="34">
         <v>10.32</v>
       </c>
-      <c r="J68" s="33">
+      <c r="J68" s="34">
         <v>9.35</v>
       </c>
-      <c r="K68" s="33">
+      <c r="K68" s="34">
         <v>10.14</v>
       </c>
-      <c r="L68" s="33">
+      <c r="L68" s="34">
         <v>9.59</v>
       </c>
-      <c r="M68" s="33">
+      <c r="M68" s="34">
         <v>13.85</v>
       </c>
-      <c r="N68" s="33">
+      <c r="N68" s="34">
         <v>20.12</v>
       </c>
-      <c r="O68" s="33">
+      <c r="O68" s="34">
         <v>4.74</v>
       </c>
-      <c r="P68" s="33">
+      <c r="P68" s="34">
         <v>4.53</v>
       </c>
-      <c r="Q68" s="33">
+      <c r="Q68" s="34">
         <v>7.78</v>
       </c>
-      <c r="R68" s="33">
+      <c r="R68" s="34">
         <v>4.51</v>
       </c>
-      <c r="S68" s="33">
+      <c r="S68" s="34">
         <v>8.19</v>
       </c>
-      <c r="T68" s="33">
+      <c r="T68" s="34">
         <v>11.11</v>
       </c>
-      <c r="U68" s="33">
+      <c r="U68" s="34">
         <v>19.1</v>
       </c>
-      <c r="V68" s="33">
+      <c r="V68" s="34">
         <v>6.32</v>
       </c>
-      <c r="W68" s="33">
+      <c r="W68" s="34">
         <v>5.39</v>
       </c>
-      <c r="X68" s="33">
+      <c r="X68" s="34">
         <v>5.45</v>
       </c>
-      <c r="Y68" s="33">
+      <c r="Y68" s="34">
         <v>4.64</v>
       </c>
-      <c r="Z68" s="31"/>
+      <c r="Z68" s="32"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="30" t="s">
-        <v>466</v>
-      </c>
-      <c r="B69" s="33">
+      <c r="A69" s="31" t="s">
+        <v>467</v>
+      </c>
+      <c r="B69" s="34">
         <v>8.79</v>
       </c>
-      <c r="C69" s="33">
+      <c r="C69" s="34">
         <v>8.96</v>
       </c>
-      <c r="D69" s="33">
+      <c r="D69" s="34">
         <v>9.34</v>
       </c>
-      <c r="E69" s="33">
+      <c r="E69" s="34">
         <v>11.56</v>
       </c>
-      <c r="F69" s="33">
+      <c r="F69" s="34">
         <v>11.42</v>
       </c>
-      <c r="G69" s="33">
+      <c r="G69" s="34">
         <v>10.59</v>
       </c>
-      <c r="H69" s="33">
+      <c r="H69" s="34">
         <v>10.21</v>
       </c>
-      <c r="I69" s="33">
+      <c r="I69" s="34">
         <v>10.3</v>
       </c>
-      <c r="J69" s="33">
+      <c r="J69" s="34">
         <v>11.04</v>
       </c>
-      <c r="K69" s="33">
+      <c r="K69" s="34">
         <v>10.88</v>
       </c>
-      <c r="L69" s="33">
+      <c r="L69" s="34">
         <v>10.16</v>
       </c>
-      <c r="M69" s="33">
+      <c r="M69" s="34">
         <v>10.12</v>
       </c>
-      <c r="N69" s="33">
+      <c r="N69" s="34">
         <v>8.04</v>
       </c>
-      <c r="O69" s="33">
+      <c r="O69" s="34">
         <v>5.66</v>
       </c>
-      <c r="P69" s="33">
+      <c r="P69" s="34">
         <v>6.87</v>
       </c>
-      <c r="Q69" s="33">
+      <c r="Q69" s="34">
         <v>9.18</v>
       </c>
-      <c r="R69" s="33">
+      <c r="R69" s="34">
         <v>8.61</v>
       </c>
-      <c r="S69" s="33">
+      <c r="S69" s="34">
         <v>8.35</v>
       </c>
-      <c r="T69" s="33">
+      <c r="T69" s="34">
         <v>7.62</v>
       </c>
-      <c r="U69" s="33">
+      <c r="U69" s="34">
         <v>6.43</v>
       </c>
-      <c r="V69" s="31"/>
-      <c r="W69" s="31"/>
-      <c r="X69" s="31"/>
-      <c r="Y69" s="31"/>
-      <c r="Z69" s="31"/>
+      <c r="V69" s="32"/>
+      <c r="W69" s="32"/>
+      <c r="X69" s="32"/>
+      <c r="Y69" s="32"/>
+      <c r="Z69" s="32"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="28" t="s">
-        <v>467</v>
-      </c>
-      <c r="B70" s="29"/>
-      <c r="C70" s="29"/>
-      <c r="D70" s="29"/>
-      <c r="E70" s="29"/>
-      <c r="F70" s="29"/>
-      <c r="G70" s="29"/>
-      <c r="H70" s="29"/>
-      <c r="I70" s="29"/>
-      <c r="J70" s="29"/>
-      <c r="K70" s="29"/>
-      <c r="L70" s="29"/>
-      <c r="M70" s="29"/>
-      <c r="N70" s="29"/>
-      <c r="O70" s="29"/>
-      <c r="P70" s="29"/>
-      <c r="Q70" s="29"/>
-      <c r="R70" s="29"/>
-      <c r="S70" s="29"/>
-      <c r="T70" s="29"/>
-      <c r="U70" s="29"/>
-      <c r="V70" s="29"/>
-      <c r="W70" s="29"/>
-      <c r="X70" s="29"/>
-      <c r="Y70" s="29"/>
-      <c r="Z70" s="29"/>
+      <c r="A70" s="29" t="s">
+        <v>468</v>
+      </c>
+      <c r="B70" s="30"/>
+      <c r="C70" s="30"/>
+      <c r="D70" s="30"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="30"/>
+      <c r="H70" s="30"/>
+      <c r="I70" s="30"/>
+      <c r="J70" s="30"/>
+      <c r="K70" s="30"/>
+      <c r="L70" s="30"/>
+      <c r="M70" s="30"/>
+      <c r="N70" s="30"/>
+      <c r="O70" s="30"/>
+      <c r="P70" s="30"/>
+      <c r="Q70" s="30"/>
+      <c r="R70" s="30"/>
+      <c r="S70" s="30"/>
+      <c r="T70" s="30"/>
+      <c r="U70" s="30"/>
+      <c r="V70" s="30"/>
+      <c r="W70" s="30"/>
+      <c r="X70" s="30"/>
+      <c r="Y70" s="30"/>
+      <c r="Z70" s="30"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="30" t="s">
-        <v>468</v>
-      </c>
-      <c r="B71" s="33">
+      <c r="A71" s="31" t="s">
+        <v>469</v>
+      </c>
+      <c r="B71" s="34">
         <v>51.8</v>
       </c>
-      <c r="C71" s="32">
+      <c r="C71" s="33">
         <v>272.87</v>
       </c>
-      <c r="D71" s="33">
+      <c r="D71" s="34">
         <v>10.04</v>
       </c>
-      <c r="E71" s="33">
+      <c r="E71" s="34">
         <v>16.36</v>
       </c>
-      <c r="F71" s="33">
+      <c r="F71" s="34">
         <v>32.25</v>
       </c>
-      <c r="G71" s="31"/>
-      <c r="H71" s="31"/>
-      <c r="I71" s="31"/>
-      <c r="J71" s="33">
+      <c r="G71" s="32"/>
+      <c r="H71" s="32"/>
+      <c r="I71" s="32"/>
+      <c r="J71" s="34">
         <v>16.38</v>
       </c>
-      <c r="K71" s="33">
+      <c r="K71" s="34">
         <v>18.68</v>
       </c>
-      <c r="L71" s="33">
+      <c r="L71" s="34">
         <v>17.23</v>
       </c>
-      <c r="M71" s="33">
+      <c r="M71" s="34">
         <v>55.36</v>
       </c>
-      <c r="N71" s="32">
+      <c r="N71" s="33">
         <v>428.88</v>
       </c>
-      <c r="O71" s="33">
+      <c r="O71" s="34">
         <v>7.47</v>
       </c>
-      <c r="P71" s="33">
+      <c r="P71" s="34">
         <v>5.96</v>
       </c>
-      <c r="Q71" s="33">
+      <c r="Q71" s="34">
         <v>11.39</v>
       </c>
-      <c r="R71" s="33">
+      <c r="R71" s="34">
         <v>19.37</v>
       </c>
-      <c r="S71" s="33">
+      <c r="S71" s="34">
         <v>77.68</v>
       </c>
-      <c r="T71" s="33">
+      <c r="T71" s="34">
         <v>58.41</v>
       </c>
-      <c r="U71" s="31"/>
-      <c r="V71" s="33">
+      <c r="U71" s="32"/>
+      <c r="V71" s="34">
         <v>11.92</v>
       </c>
-      <c r="W71" s="33">
+      <c r="W71" s="34">
         <v>7.47</v>
       </c>
-      <c r="X71" s="33">
+      <c r="X71" s="34">
         <v>7.55</v>
       </c>
-      <c r="Y71" s="33">
+      <c r="Y71" s="34">
         <v>7.11</v>
       </c>
-      <c r="Z71" s="31"/>
+      <c r="Z71" s="32"/>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="30" t="s">
-        <v>469</v>
-      </c>
-      <c r="B72" s="33">
+      <c r="A72" s="31" t="s">
+        <v>470</v>
+      </c>
+      <c r="B72" s="34">
         <v>22.25</v>
       </c>
-      <c r="C72" s="33">
+      <c r="C72" s="34">
         <v>25.68</v>
       </c>
-      <c r="D72" s="33">
+      <c r="D72" s="34">
         <v>44.16</v>
       </c>
-      <c r="E72" s="31"/>
-      <c r="F72" s="31"/>
-      <c r="G72" s="32">
+      <c r="E72" s="32"/>
+      <c r="F72" s="32"/>
+      <c r="G72" s="33">
         <v>2223.07</v>
       </c>
-      <c r="H72" s="33">
+      <c r="H72" s="34">
         <v>70.76</v>
       </c>
-      <c r="I72" s="33">
+      <c r="I72" s="34">
         <v>29.68</v>
       </c>
-      <c r="J72" s="33">
+      <c r="J72" s="34">
         <v>23.12</v>
       </c>
-      <c r="K72" s="33">
+      <c r="K72" s="34">
         <v>23.48</v>
       </c>
-      <c r="L72" s="33">
+      <c r="L72" s="34">
         <v>21.27</v>
       </c>
-      <c r="M72" s="33">
+      <c r="M72" s="34">
         <v>21.69</v>
       </c>
-      <c r="N72" s="33">
+      <c r="N72" s="34">
         <v>15.94</v>
       </c>
-      <c r="O72" s="33">
+      <c r="O72" s="34">
         <v>10.53</v>
       </c>
-      <c r="P72" s="33">
+      <c r="P72" s="34">
         <v>15.25</v>
       </c>
-      <c r="Q72" s="33">
+      <c r="Q72" s="34">
         <v>98.78</v>
       </c>
-      <c r="R72" s="33">
+      <c r="R72" s="34">
         <v>86.5</v>
       </c>
-      <c r="S72" s="33">
+      <c r="S72" s="34">
         <v>31.48</v>
       </c>
-      <c r="T72" s="33">
+      <c r="T72" s="34">
         <v>18.7</v>
       </c>
-      <c r="U72" s="33">
+      <c r="U72" s="34">
         <v>13.0</v>
       </c>
-      <c r="V72" s="31"/>
-      <c r="W72" s="31"/>
-      <c r="X72" s="31"/>
-      <c r="Y72" s="31"/>
-      <c r="Z72" s="31"/>
+      <c r="V72" s="32"/>
+      <c r="W72" s="32"/>
+      <c r="X72" s="32"/>
+      <c r="Y72" s="32"/>
+      <c r="Z72" s="32"/>
     </row>
     <row r="73" ht="15.75" customHeight="1"/>
     <row r="74" ht="15.75" customHeight="1"/>
